--- a/research/traditional_assets/database/data/philippines/philippines_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_healthcare_support_services.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1024298243320623</v>
+        <v>0.1022074997712321</v>
       </c>
       <c r="C2">
-        <v>19.43817590889865</v>
+        <v>19.27371320685536</v>
       </c>
       <c r="D2">
-        <v>18.88617590889865</v>
+        <v>18.91871320685536</v>
       </c>
       <c r="E2">
-        <v>-4.999999999999999</v>
+        <v>-4.802999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="G2">
         <v>0.552</v>
@@ -1433,28 +1433,28 @@
         <v>3.581</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.009909100000000001</v>
       </c>
       <c r="N2">
-        <v>3.581</v>
+        <v>3.5710909</v>
       </c>
       <c r="O2">
-        <v>0.89525</v>
+        <v>0.892772725</v>
       </c>
       <c r="P2">
-        <v>2.68575</v>
+        <v>2.678318175</v>
       </c>
       <c r="Q2">
-        <v>2.91475</v>
+        <v>2.907318175</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1024298243320623</v>
+        <v>0.1028588381527597</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738455</v>
+        <v>0.8302756192024353</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>361.3849895550554</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1022074997712321</v>
+        <v>0.101985175210402</v>
       </c>
       <c r="C3">
-        <v>19.27371320685536</v>
+        <v>19.10936280947434</v>
       </c>
       <c r="D3">
-        <v>18.91871320685536</v>
+        <v>18.95136280947434</v>
       </c>
       <c r="E3">
-        <v>-4.802999999999999</v>
+        <v>-4.605999999999999</v>
       </c>
       <c r="F3">
-        <v>0.197</v>
+        <v>0.394</v>
       </c>
       <c r="G3">
         <v>0.552</v>
@@ -1515,28 +1515,28 @@
         <v>3.581</v>
       </c>
       <c r="M3">
-        <v>0.009909100000000001</v>
+        <v>0.0198182</v>
       </c>
       <c r="N3">
-        <v>3.5710909</v>
+        <v>3.5611818</v>
       </c>
       <c r="O3">
-        <v>0.892772725</v>
+        <v>0.89029545</v>
       </c>
       <c r="P3">
-        <v>2.678318175</v>
+        <v>2.67088635</v>
       </c>
       <c r="Q3">
-        <v>2.907318175</v>
+        <v>2.89988635</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1028588381527597</v>
+        <v>0.1032966073575531</v>
       </c>
       <c r="T3">
-        <v>0.8302756192024353</v>
+        <v>0.836645694537731</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>361.3849895550554</v>
+        <v>180.6924947775277</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.101985175210402</v>
+        <v>0.1017628506495718</v>
       </c>
       <c r="C4">
-        <v>19.10936280947434</v>
+        <v>18.94512529920135</v>
       </c>
       <c r="D4">
-        <v>18.95136280947434</v>
+        <v>18.98412529920135</v>
       </c>
       <c r="E4">
-        <v>-4.605999999999999</v>
+        <v>-4.408999999999999</v>
       </c>
       <c r="F4">
-        <v>0.394</v>
+        <v>0.591</v>
       </c>
       <c r="G4">
         <v>0.552</v>
@@ -1597,28 +1597,28 @@
         <v>3.581</v>
       </c>
       <c r="M4">
-        <v>0.0198182</v>
+        <v>0.0297273</v>
       </c>
       <c r="N4">
-        <v>3.5611818</v>
+        <v>3.5512727</v>
       </c>
       <c r="O4">
-        <v>0.89029545</v>
+        <v>0.887818175</v>
       </c>
       <c r="P4">
-        <v>2.67088635</v>
+        <v>2.663454525</v>
       </c>
       <c r="Q4">
-        <v>2.89988635</v>
+        <v>2.892454525</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1032966073575531</v>
+        <v>0.1037434027315173</v>
       </c>
       <c r="T4">
-        <v>0.836645694537731</v>
+        <v>0.8431471116325171</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>180.6924947775277</v>
+        <v>120.4616631850185</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1017628506495718</v>
+        <v>0.1015405260887417</v>
       </c>
       <c r="C5">
-        <v>18.94512529920135</v>
+        <v>18.78100126251678</v>
       </c>
       <c r="D5">
-        <v>18.98412529920135</v>
+        <v>19.01700126251678</v>
       </c>
       <c r="E5">
-        <v>-4.408999999999999</v>
+        <v>-4.211999999999999</v>
       </c>
       <c r="F5">
-        <v>0.591</v>
+        <v>0.788</v>
       </c>
       <c r="G5">
         <v>0.552</v>
@@ -1679,28 +1679,28 @@
         <v>3.581</v>
       </c>
       <c r="M5">
-        <v>0.0297273</v>
+        <v>0.0396364</v>
       </c>
       <c r="N5">
-        <v>3.5512727</v>
+        <v>3.5413636</v>
       </c>
       <c r="O5">
-        <v>0.887818175</v>
+        <v>0.8853409</v>
       </c>
       <c r="P5">
-        <v>2.663454525</v>
+        <v>2.6560227</v>
       </c>
       <c r="Q5">
-        <v>2.892454525</v>
+        <v>2.8850227</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1037434027315173</v>
+        <v>0.1041995063424392</v>
       </c>
       <c r="T5">
-        <v>0.8431471116325171</v>
+        <v>0.8497839749167782</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>120.4616631850185</v>
+        <v>90.34624738876386</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1015405260887417</v>
+        <v>0.1013182015279115</v>
       </c>
       <c r="C6">
-        <v>18.78100126251678</v>
+        <v>18.61699128997065</v>
       </c>
       <c r="D6">
-        <v>19.01700126251678</v>
+        <v>19.04999128997065</v>
       </c>
       <c r="E6">
-        <v>-4.211999999999999</v>
+        <v>-4.014999999999999</v>
       </c>
       <c r="F6">
-        <v>0.788</v>
+        <v>0.985</v>
       </c>
       <c r="G6">
         <v>0.552</v>
@@ -1761,28 +1761,28 @@
         <v>3.581</v>
       </c>
       <c r="M6">
-        <v>0.0396364</v>
+        <v>0.0495455</v>
       </c>
       <c r="N6">
-        <v>3.5413636</v>
+        <v>3.5314545</v>
       </c>
       <c r="O6">
-        <v>0.8853409</v>
+        <v>0.882863625</v>
       </c>
       <c r="P6">
-        <v>2.6560227</v>
+        <v>2.648590875</v>
       </c>
       <c r="Q6">
-        <v>2.8850227</v>
+        <v>2.877590875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1041995063424392</v>
+        <v>0.1046652121346437</v>
       </c>
       <c r="T6">
-        <v>0.8497839749167782</v>
+        <v>0.8565605616386026</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>90.34624738876386</v>
+        <v>72.27699791101109</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1013182015279115</v>
+        <v>0.1010958769670813</v>
       </c>
       <c r="C7">
-        <v>18.61699128997065</v>
+        <v>18.45309597621796</v>
       </c>
       <c r="D7">
-        <v>19.04999128997065</v>
+        <v>19.08309597621796</v>
       </c>
       <c r="E7">
-        <v>-4.014999999999999</v>
+        <v>-3.817999999999999</v>
       </c>
       <c r="F7">
-        <v>0.985</v>
+        <v>1.182</v>
       </c>
       <c r="G7">
         <v>0.552</v>
@@ -1843,28 +1843,28 @@
         <v>3.581</v>
       </c>
       <c r="M7">
-        <v>0.0495455</v>
+        <v>0.0594546</v>
       </c>
       <c r="N7">
-        <v>3.5314545</v>
+        <v>3.5215454</v>
       </c>
       <c r="O7">
-        <v>0.882863625</v>
+        <v>0.88038635</v>
       </c>
       <c r="P7">
-        <v>2.648590875</v>
+        <v>2.64115905</v>
       </c>
       <c r="Q7">
-        <v>2.877590875</v>
+        <v>2.87015905</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1046652121346437</v>
+        <v>0.1051408265607248</v>
       </c>
       <c r="T7">
-        <v>0.8565605616386026</v>
+        <v>0.863481331056636</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>72.27699791101109</v>
+        <v>60.23083159250925</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1010958769670813</v>
+        <v>0.1008735524062512</v>
       </c>
       <c r="C8">
-        <v>18.45309597621796</v>
+        <v>18.28931592005441</v>
       </c>
       <c r="D8">
-        <v>19.08309597621796</v>
+        <v>19.11631592005441</v>
       </c>
       <c r="E8">
-        <v>-3.817999999999999</v>
+        <v>-3.621</v>
       </c>
       <c r="F8">
-        <v>1.182</v>
+        <v>1.379</v>
       </c>
       <c r="G8">
         <v>0.552</v>
@@ -1925,28 +1925,28 @@
         <v>3.581</v>
       </c>
       <c r="M8">
-        <v>0.0594546</v>
+        <v>0.06936369999999999</v>
       </c>
       <c r="N8">
-        <v>3.5215454</v>
+        <v>3.5116363</v>
       </c>
       <c r="O8">
-        <v>0.88038635</v>
+        <v>0.877909075</v>
       </c>
       <c r="P8">
-        <v>2.64115905</v>
+        <v>2.633727225</v>
       </c>
       <c r="Q8">
-        <v>2.87015905</v>
+        <v>2.862727225</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1051408265607248</v>
+        <v>0.1056266692540336</v>
       </c>
       <c r="T8">
-        <v>0.863481331056636</v>
+        <v>0.8705509342255948</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>60.23083159250925</v>
+        <v>51.62642707929365</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1008735524062512</v>
+        <v>0.100651227845421</v>
       </c>
       <c r="C9">
-        <v>18.28931592005441</v>
+        <v>18.12565172445254</v>
       </c>
       <c r="D9">
-        <v>19.11631592005442</v>
+        <v>19.14965172445254</v>
       </c>
       <c r="E9">
-        <v>-3.620999999999999</v>
+        <v>-3.423999999999999</v>
       </c>
       <c r="F9">
-        <v>1.379</v>
+        <v>1.576</v>
       </c>
       <c r="G9">
         <v>0.552</v>
@@ -2007,28 +2007,28 @@
         <v>3.581</v>
       </c>
       <c r="M9">
-        <v>0.0693637</v>
+        <v>0.0792728</v>
       </c>
       <c r="N9">
-        <v>3.5116363</v>
+        <v>3.5017272</v>
       </c>
       <c r="O9">
-        <v>0.877909075</v>
+        <v>0.8754318</v>
       </c>
       <c r="P9">
-        <v>2.633727225</v>
+        <v>2.6262954</v>
       </c>
       <c r="Q9">
-        <v>2.862727225</v>
+        <v>2.8552954</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1056266692540336</v>
+        <v>0.1061230737450229</v>
       </c>
       <c r="T9">
-        <v>0.8705509342255948</v>
+        <v>0.877774224419966</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.62642707929364</v>
+        <v>45.17312369438193</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.100651227845421</v>
+        <v>0.1004289032845909</v>
       </c>
       <c r="C10">
-        <v>18.12565172445254</v>
+        <v>17.96210399659818</v>
       </c>
       <c r="D10">
-        <v>19.14965172445254</v>
+        <v>19.18310399659818</v>
       </c>
       <c r="E10">
-        <v>-3.423999999999999</v>
+        <v>-3.226999999999999</v>
       </c>
       <c r="F10">
-        <v>1.576</v>
+        <v>1.773</v>
       </c>
       <c r="G10">
         <v>0.552</v>
@@ -2089,28 +2089,28 @@
         <v>3.581</v>
       </c>
       <c r="M10">
-        <v>0.0792728</v>
+        <v>0.08918189999999999</v>
       </c>
       <c r="N10">
-        <v>3.5017272</v>
+        <v>3.4918181</v>
       </c>
       <c r="O10">
-        <v>0.8754318</v>
+        <v>0.872954525</v>
       </c>
       <c r="P10">
-        <v>2.6262954</v>
+        <v>2.618863575</v>
       </c>
       <c r="Q10">
-        <v>2.8552954</v>
+        <v>2.847863575</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1061230737450229</v>
+        <v>0.1066303882248252</v>
       </c>
       <c r="T10">
-        <v>0.877774224419966</v>
+        <v>0.8851562682449824</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>45.17312369438193</v>
+        <v>40.1538877283395</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1004289032845909</v>
+        <v>0.1002065787237607</v>
       </c>
       <c r="C11">
-        <v>17.96210399659818</v>
+        <v>17.79867334792732</v>
       </c>
       <c r="D11">
-        <v>19.18310399659818</v>
+        <v>19.21667334792732</v>
       </c>
       <c r="E11">
-        <v>-3.226999999999999</v>
+        <v>-3.029999999999999</v>
       </c>
       <c r="F11">
-        <v>1.773</v>
+        <v>1.97</v>
       </c>
       <c r="G11">
         <v>0.552</v>
@@ -2171,28 +2171,28 @@
         <v>3.581</v>
       </c>
       <c r="M11">
-        <v>0.08918189999999999</v>
+        <v>0.09909099999999998</v>
       </c>
       <c r="N11">
-        <v>3.4918181</v>
+        <v>3.481909</v>
       </c>
       <c r="O11">
-        <v>0.872954525</v>
+        <v>0.87047725</v>
       </c>
       <c r="P11">
-        <v>2.618863575</v>
+        <v>2.61143175</v>
       </c>
       <c r="Q11">
-        <v>2.847863575</v>
+        <v>2.84043175</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1066303882248252</v>
+        <v>0.1071489763597342</v>
       </c>
       <c r="T11">
-        <v>0.8851562682449824</v>
+        <v>0.8927023574883326</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.1538877283395</v>
+        <v>36.13849895550555</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1002065787237607</v>
+        <v>0.09998425416293058</v>
       </c>
       <c r="C12">
-        <v>17.79867334792732</v>
+        <v>17.63536039416336</v>
       </c>
       <c r="D12">
-        <v>19.21667334792732</v>
+        <v>19.25036039416335</v>
       </c>
       <c r="E12">
-        <v>-3.029999999999999</v>
+        <v>-2.832999999999999</v>
       </c>
       <c r="F12">
-        <v>1.97</v>
+        <v>2.167</v>
       </c>
       <c r="G12">
         <v>0.552</v>
@@ -2253,28 +2253,28 @@
         <v>3.581</v>
       </c>
       <c r="M12">
-        <v>0.099091</v>
+        <v>0.1090001</v>
       </c>
       <c r="N12">
-        <v>3.481909</v>
+        <v>3.4719999</v>
       </c>
       <c r="O12">
-        <v>0.87047725</v>
+        <v>0.867999975</v>
       </c>
       <c r="P12">
-        <v>2.61143175</v>
+        <v>2.603999925</v>
       </c>
       <c r="Q12">
-        <v>2.84043175</v>
+        <v>2.832999925</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1071489763597342</v>
+        <v>0.1076792181605962</v>
       </c>
       <c r="T12">
-        <v>0.8927023574883326</v>
+        <v>0.9004180217708594</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.13849895550555</v>
+        <v>32.85318086864141</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09998425416293058</v>
+        <v>0.09976192960210042</v>
       </c>
       <c r="C13">
-        <v>17.63536039416336</v>
+        <v>17.47216575535476</v>
       </c>
       <c r="D13">
-        <v>19.25036039416335</v>
+        <v>19.28416575535476</v>
       </c>
       <c r="E13">
-        <v>-2.832999999999999</v>
+        <v>-2.635999999999999</v>
       </c>
       <c r="F13">
-        <v>2.167</v>
+        <v>2.364</v>
       </c>
       <c r="G13">
         <v>0.552</v>
@@ -2335,28 +2335,28 @@
         <v>3.581</v>
       </c>
       <c r="M13">
-        <v>0.1090001</v>
+        <v>0.1189092</v>
       </c>
       <c r="N13">
-        <v>3.4719999</v>
+        <v>3.4620908</v>
       </c>
       <c r="O13">
-        <v>0.867999975</v>
+        <v>0.8655227</v>
       </c>
       <c r="P13">
-        <v>2.603999925</v>
+        <v>2.5965681</v>
       </c>
       <c r="Q13">
-        <v>2.832999925</v>
+        <v>2.8255681</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1076792181605962</v>
+        <v>0.1082215109114777</v>
       </c>
       <c r="T13">
-        <v>0.9004180217708594</v>
+        <v>0.908309042059807</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.85318086864141</v>
+        <v>30.11541579625462</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09976192960210042</v>
+        <v>0.09953960504127027</v>
       </c>
       <c r="C14">
-        <v>17.47216575535476</v>
+        <v>17.30909005591312</v>
       </c>
       <c r="D14">
-        <v>19.28416575535476</v>
+        <v>19.31809005591312</v>
       </c>
       <c r="E14">
-        <v>-2.635999999999999</v>
+        <v>-2.438999999999999</v>
       </c>
       <c r="F14">
-        <v>2.364</v>
+        <v>2.561</v>
       </c>
       <c r="G14">
         <v>0.552</v>
@@ -2417,28 +2417,28 @@
         <v>3.581</v>
       </c>
       <c r="M14">
-        <v>0.1189092</v>
+        <v>0.1288183</v>
       </c>
       <c r="N14">
-        <v>3.4620908</v>
+        <v>3.4521817</v>
       </c>
       <c r="O14">
-        <v>0.8655227</v>
+        <v>0.863045425</v>
       </c>
       <c r="P14">
-        <v>2.5965681</v>
+        <v>2.589136275</v>
       </c>
       <c r="Q14">
-        <v>2.8255681</v>
+        <v>2.818136275</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1082215109114777</v>
+        <v>0.1087762701623796</v>
       </c>
       <c r="T14">
-        <v>0.908309042059807</v>
+        <v>0.9163814651140179</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.11541579625462</v>
+        <v>27.79884535038888</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09953960504127027</v>
+        <v>0.09931728048044011</v>
       </c>
       <c r="C15">
-        <v>17.30909005591312</v>
+        <v>17.14613392465156</v>
       </c>
       <c r="D15">
-        <v>19.31809005591312</v>
+        <v>19.35213392465156</v>
       </c>
       <c r="E15">
-        <v>-2.438999999999999</v>
+        <v>-2.241999999999999</v>
       </c>
       <c r="F15">
-        <v>2.561</v>
+        <v>2.758</v>
       </c>
       <c r="G15">
         <v>0.552</v>
@@ -2499,28 +2499,28 @@
         <v>3.581</v>
       </c>
       <c r="M15">
-        <v>0.1288183</v>
+        <v>0.1387274</v>
       </c>
       <c r="N15">
-        <v>3.4521817</v>
+        <v>3.4422726</v>
       </c>
       <c r="O15">
-        <v>0.863045425</v>
+        <v>0.86056815</v>
       </c>
       <c r="P15">
-        <v>2.589136275</v>
+        <v>2.58170445</v>
       </c>
       <c r="Q15">
-        <v>2.818136275</v>
+        <v>2.81070445</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1087762701623796</v>
+        <v>0.1093439307912094</v>
       </c>
       <c r="T15">
-        <v>0.9163814651140179</v>
+        <v>0.9246416189369313</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.79884535038888</v>
+        <v>25.81321353964682</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09931728048044011</v>
+        <v>0.09909495591960996</v>
       </c>
       <c r="C16">
-        <v>17.14613392465156</v>
+        <v>16.98329799482359</v>
       </c>
       <c r="D16">
-        <v>19.35213392465156</v>
+        <v>19.38629799482359</v>
       </c>
       <c r="E16">
-        <v>-2.241999999999999</v>
+        <v>-2.044999999999999</v>
       </c>
       <c r="F16">
-        <v>2.758</v>
+        <v>2.955000000000001</v>
       </c>
       <c r="G16">
         <v>0.552</v>
@@ -2581,28 +2581,28 @@
         <v>3.581</v>
       </c>
       <c r="M16">
-        <v>0.1387274</v>
+        <v>0.1486365</v>
       </c>
       <c r="N16">
-        <v>3.4422726</v>
+        <v>3.4323635</v>
       </c>
       <c r="O16">
-        <v>0.86056815</v>
+        <v>0.858090875</v>
       </c>
       <c r="P16">
-        <v>2.58170445</v>
+        <v>2.574272625</v>
       </c>
       <c r="Q16">
-        <v>2.81070445</v>
+        <v>2.803272625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1093439307912094</v>
+        <v>0.1099249481407176</v>
       </c>
       <c r="T16">
-        <v>0.9246416189369313</v>
+        <v>0.9330961293203839</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.81321353964682</v>
+        <v>24.0923326370037</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09909495591960996</v>
+        <v>0.0988726313587798</v>
       </c>
       <c r="C17">
-        <v>16.98329799482359</v>
+        <v>16.82058290416242</v>
       </c>
       <c r="D17">
-        <v>19.38629799482359</v>
+        <v>19.42058290416243</v>
       </c>
       <c r="E17">
-        <v>-2.044999999999999</v>
+        <v>-1.847999999999999</v>
       </c>
       <c r="F17">
-        <v>2.955</v>
+        <v>3.152</v>
       </c>
       <c r="G17">
         <v>0.552</v>
@@ -2663,28 +2663,28 @@
         <v>3.581</v>
       </c>
       <c r="M17">
-        <v>0.1486365</v>
+        <v>0.1585456</v>
       </c>
       <c r="N17">
-        <v>3.4323635</v>
+        <v>3.4224544</v>
       </c>
       <c r="O17">
-        <v>0.858090875</v>
+        <v>0.8556136</v>
       </c>
       <c r="P17">
-        <v>2.574272625</v>
+        <v>2.5668408</v>
       </c>
       <c r="Q17">
-        <v>2.803272625</v>
+        <v>2.7958408</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1099249481407176</v>
+        <v>0.1105197992366426</v>
       </c>
       <c r="T17">
-        <v>0.9330961293203839</v>
+        <v>0.9417519375701091</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.0923326370037</v>
+        <v>22.58656184719096</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0988726313587798</v>
+        <v>0.09865030679794964</v>
       </c>
       <c r="C18">
-        <v>16.82058290416242</v>
+        <v>16.6579892949206</v>
       </c>
       <c r="D18">
-        <v>19.42058290416243</v>
+        <v>19.4549892949206</v>
       </c>
       <c r="E18">
-        <v>-1.847999999999999</v>
+        <v>-1.650999999999999</v>
       </c>
       <c r="F18">
-        <v>3.152</v>
+        <v>3.349</v>
       </c>
       <c r="G18">
         <v>0.552</v>
@@ -2745,28 +2745,28 @@
         <v>3.581</v>
       </c>
       <c r="M18">
-        <v>0.1585456</v>
+        <v>0.1684547</v>
       </c>
       <c r="N18">
-        <v>3.4224544</v>
+        <v>3.4125453</v>
       </c>
       <c r="O18">
-        <v>0.8556136</v>
+        <v>0.853136325</v>
       </c>
       <c r="P18">
-        <v>2.5668408</v>
+        <v>2.559408975</v>
       </c>
       <c r="Q18">
-        <v>2.7958408</v>
+        <v>2.788408975</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1105197992366426</v>
+        <v>0.1111289840939153</v>
       </c>
       <c r="T18">
-        <v>0.9417519375701091</v>
+        <v>0.9506163195125991</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.58656184719096</v>
+        <v>21.25794056206209</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09865030679794964</v>
+        <v>0.09842798223711949</v>
       </c>
       <c r="C19">
-        <v>16.6579892949206</v>
+        <v>16.49551781391012</v>
       </c>
       <c r="D19">
-        <v>19.4549892949206</v>
+        <v>19.48951781391012</v>
       </c>
       <c r="E19">
-        <v>-1.650999999999999</v>
+        <v>-1.453999999999999</v>
       </c>
       <c r="F19">
-        <v>3.349</v>
+        <v>3.546</v>
       </c>
       <c r="G19">
         <v>0.552</v>
@@ -2827,28 +2827,28 @@
         <v>3.581</v>
       </c>
       <c r="M19">
-        <v>0.1684547</v>
+        <v>0.1783638</v>
       </c>
       <c r="N19">
-        <v>3.4125453</v>
+        <v>3.4026362</v>
       </c>
       <c r="O19">
-        <v>0.853136325</v>
+        <v>0.85065905</v>
       </c>
       <c r="P19">
-        <v>2.559408975</v>
+        <v>2.55197715</v>
       </c>
       <c r="Q19">
-        <v>2.788408975</v>
+        <v>2.78097715</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1111289840939153</v>
+        <v>0.1117530271184384</v>
       </c>
       <c r="T19">
-        <v>0.9506163195125991</v>
+        <v>0.9596969058927103</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.25794056206209</v>
+        <v>20.07694386416975</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0984279822371195</v>
+        <v>0.09820565767628933</v>
       </c>
       <c r="C20">
-        <v>16.49551781391012</v>
+        <v>16.33316911254296</v>
       </c>
       <c r="D20">
-        <v>19.48951781391012</v>
+        <v>19.52416911254296</v>
       </c>
       <c r="E20">
-        <v>-1.453999999999999</v>
+        <v>-1.256999999999999</v>
       </c>
       <c r="F20">
-        <v>3.546</v>
+        <v>3.743</v>
       </c>
       <c r="G20">
         <v>0.552</v>
@@ -2909,28 +2909,28 @@
         <v>3.581</v>
       </c>
       <c r="M20">
-        <v>0.1783638</v>
+        <v>0.1882729</v>
       </c>
       <c r="N20">
-        <v>3.4026362</v>
+        <v>3.3927271</v>
       </c>
       <c r="O20">
-        <v>0.85065905</v>
+        <v>0.848181775</v>
       </c>
       <c r="P20">
-        <v>2.55197715</v>
+        <v>2.544545325</v>
       </c>
       <c r="Q20">
-        <v>2.78097715</v>
+        <v>2.773545325</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1117530271184384</v>
+        <v>0.1123924786127029</v>
       </c>
       <c r="T20">
-        <v>0.9596969058927103</v>
+        <v>0.9690017042822073</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.07694386416975</v>
+        <v>19.02026260816081</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09820565767628933</v>
+        <v>0.09798333311545919</v>
       </c>
       <c r="C21">
-        <v>16.33316911254296</v>
+        <v>16.17094384687205</v>
       </c>
       <c r="D21">
-        <v>19.52416911254296</v>
+        <v>19.55894384687205</v>
       </c>
       <c r="E21">
-        <v>-1.256999999999999</v>
+        <v>-1.059999999999999</v>
       </c>
       <c r="F21">
-        <v>3.743</v>
+        <v>3.94</v>
       </c>
       <c r="G21">
         <v>0.552</v>
@@ -2991,28 +2991,28 @@
         <v>3.581</v>
       </c>
       <c r="M21">
-        <v>0.1882729</v>
+        <v>0.198182</v>
       </c>
       <c r="N21">
-        <v>3.3927271</v>
+        <v>3.382818</v>
       </c>
       <c r="O21">
-        <v>0.848181775</v>
+        <v>0.8457045</v>
       </c>
       <c r="P21">
-        <v>2.544545325</v>
+        <v>2.5371135</v>
       </c>
       <c r="Q21">
-        <v>2.773545325</v>
+        <v>2.7661135</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1123924786127029</v>
+        <v>0.113047916394324</v>
       </c>
       <c r="T21">
-        <v>0.9690017042822073</v>
+        <v>0.9785391226314416</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.02026260816081</v>
+        <v>18.06924947775277</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09798333311545919</v>
+        <v>0.09776100855462902</v>
       </c>
       <c r="C22">
-        <v>16.17094384687205</v>
+        <v>16.00884267763269</v>
       </c>
       <c r="D22">
-        <v>19.55894384687205</v>
+        <v>19.59384267763269</v>
       </c>
       <c r="E22">
-        <v>-1.059999999999999</v>
+        <v>-0.8629999999999987</v>
       </c>
       <c r="F22">
-        <v>3.94</v>
+        <v>4.137</v>
       </c>
       <c r="G22">
         <v>0.552</v>
@@ -3073,28 +3073,28 @@
         <v>3.581</v>
       </c>
       <c r="M22">
-        <v>0.198182</v>
+        <v>0.2080911</v>
       </c>
       <c r="N22">
-        <v>3.382818</v>
+        <v>3.3729089</v>
       </c>
       <c r="O22">
-        <v>0.8457045</v>
+        <v>0.843227225</v>
       </c>
       <c r="P22">
-        <v>2.5371135</v>
+        <v>2.529681675</v>
       </c>
       <c r="Q22">
-        <v>2.7661135</v>
+        <v>2.758681675</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.113047916394324</v>
+        <v>0.1137199475375051</v>
       </c>
       <c r="T22">
-        <v>0.9785391226314416</v>
+        <v>0.9883179946097704</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.06924947775277</v>
+        <v>17.20880902643121</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09776100855462902</v>
+        <v>0.09753868399379886</v>
       </c>
       <c r="C23">
-        <v>16.00884267763269</v>
+        <v>15.84686627028437</v>
       </c>
       <c r="D23">
-        <v>19.59384267763269</v>
+        <v>19.62886627028437</v>
       </c>
       <c r="E23">
-        <v>-0.8629999999999995</v>
+        <v>-0.6659999999999995</v>
       </c>
       <c r="F23">
-        <v>4.137</v>
+        <v>4.334</v>
       </c>
       <c r="G23">
         <v>0.552</v>
@@ -3155,28 +3155,28 @@
         <v>3.581</v>
       </c>
       <c r="M23">
-        <v>0.2080911</v>
+        <v>0.2180002</v>
       </c>
       <c r="N23">
-        <v>3.3729089</v>
+        <v>3.3629998</v>
       </c>
       <c r="O23">
-        <v>0.843227225</v>
+        <v>0.84074995</v>
       </c>
       <c r="P23">
-        <v>2.529681675</v>
+        <v>2.52224985</v>
       </c>
       <c r="Q23">
-        <v>2.758681675</v>
+        <v>2.75124985</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1137199475375051</v>
+        <v>0.1144092102484601</v>
       </c>
       <c r="T23">
-        <v>0.9883179946097704</v>
+        <v>0.9983476068952358</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.20880902643122</v>
+        <v>16.4265904343207</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09753868399379886</v>
+        <v>0.09731635943296871</v>
       </c>
       <c r="C24">
-        <v>15.84686627028437</v>
+        <v>15.68501529505307</v>
       </c>
       <c r="D24">
-        <v>19.62886627028437</v>
+        <v>19.66401529505307</v>
       </c>
       <c r="E24">
-        <v>-0.6659999999999995</v>
+        <v>-0.4689999999999994</v>
       </c>
       <c r="F24">
-        <v>4.334</v>
+        <v>4.531</v>
       </c>
       <c r="G24">
         <v>0.552</v>
@@ -3237,28 +3237,28 @@
         <v>3.581</v>
       </c>
       <c r="M24">
-        <v>0.2180002</v>
+        <v>0.2279093</v>
       </c>
       <c r="N24">
-        <v>3.3629998</v>
+        <v>3.3530907</v>
       </c>
       <c r="O24">
-        <v>0.84074995</v>
+        <v>0.838272675</v>
       </c>
       <c r="P24">
-        <v>2.52224985</v>
+        <v>2.514818025</v>
       </c>
       <c r="Q24">
-        <v>2.75124985</v>
+        <v>2.743818025</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1144092102484601</v>
+        <v>0.1151163758869723</v>
       </c>
       <c r="T24">
-        <v>0.9983476068952358</v>
+        <v>1.008637728590714</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.4265904343207</v>
+        <v>15.7123908502198</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09731635943296871</v>
+        <v>0.09709403487213858</v>
       </c>
       <c r="C25">
-        <v>15.68501529505307</v>
+        <v>15.52329042697406</v>
       </c>
       <c r="D25">
-        <v>19.66401529505307</v>
+        <v>19.69929042697406</v>
       </c>
       <c r="E25">
-        <v>-0.4689999999999994</v>
+        <v>-0.2719999999999994</v>
       </c>
       <c r="F25">
-        <v>4.531</v>
+        <v>4.728</v>
       </c>
       <c r="G25">
         <v>0.552</v>
@@ -3319,28 +3319,28 @@
         <v>3.581</v>
       </c>
       <c r="M25">
-        <v>0.2279093</v>
+        <v>0.2378184</v>
       </c>
       <c r="N25">
-        <v>3.3530907</v>
+        <v>3.3431816</v>
       </c>
       <c r="O25">
-        <v>0.838272675</v>
+        <v>0.8357954</v>
       </c>
       <c r="P25">
-        <v>2.514818025</v>
+        <v>2.5073862</v>
       </c>
       <c r="Q25">
-        <v>2.743818025</v>
+        <v>2.7363862</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1151163758869723</v>
+        <v>0.1158421511475508</v>
       </c>
       <c r="T25">
-        <v>1.008637728590714</v>
+        <v>1.019198642962388</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.7123908502198</v>
+        <v>15.05770789812731</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09709403487213857</v>
+        <v>0.09687171031130841</v>
       </c>
       <c r="C26">
-        <v>15.52329042697406</v>
+        <v>15.36169234593503</v>
       </c>
       <c r="D26">
-        <v>19.69929042697406</v>
+        <v>19.73469234593503</v>
       </c>
       <c r="E26">
-        <v>-0.2719999999999994</v>
+        <v>-0.07499999999999929</v>
       </c>
       <c r="F26">
-        <v>4.728</v>
+        <v>4.925</v>
       </c>
       <c r="G26">
         <v>0.552</v>
@@ -3401,28 +3401,28 @@
         <v>3.581</v>
       </c>
       <c r="M26">
-        <v>0.2378184</v>
+        <v>0.2477275</v>
       </c>
       <c r="N26">
-        <v>3.3431816</v>
+        <v>3.3332725</v>
       </c>
       <c r="O26">
-        <v>0.8357954</v>
+        <v>0.833318125</v>
       </c>
       <c r="P26">
-        <v>2.5073862</v>
+        <v>2.499954375</v>
       </c>
       <c r="Q26">
-        <v>2.7363862</v>
+        <v>2.728954375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1158421511475508</v>
+        <v>0.1165872804150779</v>
       </c>
       <c r="T26">
-        <v>1.019198642962388</v>
+        <v>1.030041181717307</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.05770789812731</v>
+        <v>14.45539958220222</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09687171031130841</v>
+        <v>0.09664938575047824</v>
       </c>
       <c r="C27">
-        <v>15.36169234593503</v>
+        <v>15.20022173671988</v>
       </c>
       <c r="D27">
-        <v>19.73469234593503</v>
+        <v>19.77022173671988</v>
       </c>
       <c r="E27">
-        <v>-0.07499999999999929</v>
+        <v>0.1220000000000008</v>
       </c>
       <c r="F27">
-        <v>4.925</v>
+        <v>5.122</v>
       </c>
       <c r="G27">
         <v>0.552</v>
@@ -3483,28 +3483,28 @@
         <v>3.581</v>
       </c>
       <c r="M27">
-        <v>0.2477275</v>
+        <v>0.2576366</v>
       </c>
       <c r="N27">
-        <v>3.3332725</v>
+        <v>3.3233634</v>
       </c>
       <c r="O27">
-        <v>0.833318125</v>
+        <v>0.83084085</v>
       </c>
       <c r="P27">
-        <v>2.499954375</v>
+        <v>2.49252255</v>
       </c>
       <c r="Q27">
-        <v>2.728954375</v>
+        <v>2.72152255</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1165872804150779</v>
+        <v>0.1173525483114571</v>
       </c>
       <c r="T27">
-        <v>1.030041181717307</v>
+        <v>1.041176762060197</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.45539958220222</v>
+        <v>13.89942267519444</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09664938575047824</v>
+        <v>0.09642706118964808</v>
       </c>
       <c r="C28">
-        <v>15.20022173671988</v>
+        <v>15.03887928905274</v>
       </c>
       <c r="D28">
-        <v>19.77022173671988</v>
+        <v>19.80587928905274</v>
       </c>
       <c r="E28">
-        <v>0.1220000000000008</v>
+        <v>0.3190000000000008</v>
       </c>
       <c r="F28">
-        <v>5.122</v>
+        <v>5.319</v>
       </c>
       <c r="G28">
         <v>0.552</v>
@@ -3565,28 +3565,28 @@
         <v>3.581</v>
       </c>
       <c r="M28">
-        <v>0.2576366</v>
+        <v>0.2675457</v>
       </c>
       <c r="N28">
-        <v>3.3233634</v>
+        <v>3.3134543</v>
       </c>
       <c r="O28">
-        <v>0.83084085</v>
+        <v>0.828363575</v>
       </c>
       <c r="P28">
-        <v>2.49252255</v>
+        <v>2.485090725</v>
       </c>
       <c r="Q28">
-        <v>2.72152255</v>
+        <v>2.714090725</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1173525483114571</v>
+        <v>0.1181387824515727</v>
       </c>
       <c r="T28">
-        <v>1.041176762060197</v>
+        <v>1.052617426796042</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.89942267519444</v>
+        <v>13.38462924277983</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09642706118964808</v>
+        <v>0.09620473662881794</v>
       </c>
       <c r="C29">
-        <v>15.03887928905274</v>
+        <v>14.87766569764271</v>
       </c>
       <c r="D29">
-        <v>19.80587928905274</v>
+        <v>19.84166569764271</v>
       </c>
       <c r="E29">
-        <v>0.3190000000000008</v>
+        <v>0.5160000000000009</v>
       </c>
       <c r="F29">
-        <v>5.319</v>
+        <v>5.516</v>
       </c>
       <c r="G29">
         <v>0.552</v>
@@ -3647,28 +3647,28 @@
         <v>3.581</v>
       </c>
       <c r="M29">
-        <v>0.2675457</v>
+        <v>0.2774548</v>
       </c>
       <c r="N29">
-        <v>3.3134543</v>
+        <v>3.3035452</v>
       </c>
       <c r="O29">
-        <v>0.828363575</v>
+        <v>0.8258863</v>
       </c>
       <c r="P29">
-        <v>2.485090725</v>
+        <v>2.4776589</v>
       </c>
       <c r="Q29">
-        <v>2.714090725</v>
+        <v>2.7066589</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1181387824515727</v>
+        <v>0.1189468564289138</v>
       </c>
       <c r="T29">
-        <v>1.052617426796042</v>
+        <v>1.064375887774551</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.38462924277983</v>
+        <v>12.90660676982341</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09620473662881794</v>
+        <v>0.09630866206798777</v>
       </c>
       <c r="C30">
-        <v>14.87766569764271</v>
+        <v>14.66392128626178</v>
       </c>
       <c r="D30">
-        <v>19.84166569764271</v>
+        <v>19.82492128626178</v>
       </c>
       <c r="E30">
-        <v>0.5160000000000009</v>
+        <v>0.713000000000001</v>
       </c>
       <c r="F30">
-        <v>5.516</v>
+        <v>5.713</v>
       </c>
       <c r="G30">
         <v>0.552</v>
@@ -3729,45 +3729,45 @@
         <v>3.581</v>
       </c>
       <c r="M30">
-        <v>0.2774548</v>
+        <v>0.2959334</v>
       </c>
       <c r="N30">
-        <v>3.3035452</v>
+        <v>3.2850666</v>
       </c>
       <c r="O30">
-        <v>0.8258863</v>
+        <v>0.82126665</v>
       </c>
       <c r="P30">
-        <v>2.4776589</v>
+        <v>2.46379995</v>
       </c>
       <c r="Q30">
-        <v>2.7066589</v>
+        <v>2.69279995</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1189468564289138</v>
+        <v>0.1197776930535039</v>
       </c>
       <c r="T30">
-        <v>1.064375887774551</v>
+        <v>1.076465573005974</v>
       </c>
       <c r="U30">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>12.90660676982341</v>
+        <v>12.10069562948961</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09630866206798777</v>
+        <v>0.09609758750715761</v>
       </c>
       <c r="C31">
-        <v>14.66392128626178</v>
+        <v>14.50095914765846</v>
       </c>
       <c r="D31">
-        <v>19.82492128626178</v>
+        <v>19.85895914765846</v>
       </c>
       <c r="E31">
-        <v>0.7130000000000001</v>
+        <v>0.9100000000000001</v>
       </c>
       <c r="F31">
-        <v>5.712999999999999</v>
+        <v>5.909999999999999</v>
       </c>
       <c r="G31">
         <v>0.552</v>
@@ -3811,28 +3811,28 @@
         <v>3.581</v>
       </c>
       <c r="M31">
-        <v>0.2959334</v>
+        <v>0.306138</v>
       </c>
       <c r="N31">
-        <v>3.2850666</v>
+        <v>3.274862</v>
       </c>
       <c r="O31">
-        <v>0.82126665</v>
+        <v>0.8187155</v>
       </c>
       <c r="P31">
-        <v>2.46379995</v>
+        <v>2.4561465</v>
       </c>
       <c r="Q31">
-        <v>2.69279995</v>
+        <v>2.6851465</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1197776930535039</v>
+        <v>0.120632267867368</v>
       </c>
       <c r="T31">
-        <v>1.076465573005974</v>
+        <v>1.088900677815439</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.10069562948961</v>
+        <v>11.69733910850662</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09609758750715761</v>
+        <v>0.09588651294632747</v>
       </c>
       <c r="C32">
-        <v>14.50095914765846</v>
+        <v>14.3381140908431</v>
       </c>
       <c r="D32">
-        <v>19.85895914765846</v>
+        <v>19.8931140908431</v>
       </c>
       <c r="E32">
-        <v>0.9100000000000001</v>
+        <v>1.107</v>
       </c>
       <c r="F32">
-        <v>5.909999999999999</v>
+        <v>6.106999999999999</v>
       </c>
       <c r="G32">
         <v>0.552</v>
@@ -3893,28 +3893,28 @@
         <v>3.581</v>
       </c>
       <c r="M32">
-        <v>0.306138</v>
+        <v>0.3163426</v>
       </c>
       <c r="N32">
-        <v>3.274862</v>
+        <v>3.2646574</v>
       </c>
       <c r="O32">
-        <v>0.8187155</v>
+        <v>0.81616435</v>
       </c>
       <c r="P32">
-        <v>2.4561465</v>
+        <v>2.44849305</v>
       </c>
       <c r="Q32">
-        <v>2.6851465</v>
+        <v>2.67749305</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.120632267867368</v>
+        <v>0.121511612965692</v>
       </c>
       <c r="T32">
-        <v>1.088900677815439</v>
+        <v>1.101696220445467</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.69733910850662</v>
+        <v>11.32000558887738</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09588651294632747</v>
+        <v>0.0956754383854973</v>
       </c>
       <c r="C33">
-        <v>14.3381140908431</v>
+        <v>14.17538672095488</v>
       </c>
       <c r="D33">
-        <v>19.8931140908431</v>
+        <v>19.92738672095488</v>
       </c>
       <c r="E33">
-        <v>1.107</v>
+        <v>1.304000000000001</v>
       </c>
       <c r="F33">
-        <v>6.106999999999999</v>
+        <v>6.304</v>
       </c>
       <c r="G33">
         <v>0.552</v>
@@ -3975,28 +3975,28 @@
         <v>3.581</v>
       </c>
       <c r="M33">
-        <v>0.3163426</v>
+        <v>0.3265472</v>
       </c>
       <c r="N33">
-        <v>3.2646574</v>
+        <v>3.2544528</v>
       </c>
       <c r="O33">
-        <v>0.81616435</v>
+        <v>0.8136132</v>
       </c>
       <c r="P33">
-        <v>2.44849305</v>
+        <v>2.4408396</v>
       </c>
       <c r="Q33">
-        <v>2.67749305</v>
+        <v>2.6698396</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.121511612965692</v>
+        <v>0.1224168211551431</v>
       </c>
       <c r="T33">
-        <v>1.101696220445467</v>
+        <v>1.114868102564615</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.32000558887738</v>
+        <v>10.96625541422496</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0956754383854973</v>
+        <v>0.09546436382466716</v>
       </c>
       <c r="C34">
-        <v>14.17538672095488</v>
+        <v>14.01277764731038</v>
       </c>
       <c r="D34">
-        <v>19.92738672095488</v>
+        <v>19.96177764731038</v>
       </c>
       <c r="E34">
-        <v>1.304000000000001</v>
+        <v>1.501000000000001</v>
       </c>
       <c r="F34">
-        <v>6.304</v>
+        <v>6.501</v>
       </c>
       <c r="G34">
         <v>0.552</v>
@@ -4057,28 +4057,28 @@
         <v>3.581</v>
       </c>
       <c r="M34">
-        <v>0.3265472</v>
+        <v>0.3367518</v>
       </c>
       <c r="N34">
-        <v>3.2544528</v>
+        <v>3.2442482</v>
       </c>
       <c r="O34">
-        <v>0.8136132</v>
+        <v>0.81106205</v>
       </c>
       <c r="P34">
-        <v>2.4408396</v>
+        <v>2.43318615</v>
       </c>
       <c r="Q34">
-        <v>2.6698396</v>
+        <v>2.66218615</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1224168211551431</v>
+        <v>0.1233490504845779</v>
       </c>
       <c r="T34">
-        <v>1.114868102564615</v>
+        <v>1.128433175194781</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.96625541422496</v>
+        <v>10.63394464409693</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09546436382466716</v>
+        <v>0.095253289263837</v>
       </c>
       <c r="C35">
-        <v>14.01277764731038</v>
+        <v>13.85028748343974</v>
       </c>
       <c r="D35">
-        <v>19.96177764731038</v>
+        <v>19.99628748343974</v>
       </c>
       <c r="E35">
-        <v>1.501000000000001</v>
+        <v>1.698000000000001</v>
       </c>
       <c r="F35">
-        <v>6.501</v>
+        <v>6.698</v>
       </c>
       <c r="G35">
         <v>0.552</v>
@@ -4139,28 +4139,28 @@
         <v>3.581</v>
       </c>
       <c r="M35">
-        <v>0.3367518</v>
+        <v>0.3469564</v>
       </c>
       <c r="N35">
-        <v>3.2442482</v>
+        <v>3.2340436</v>
       </c>
       <c r="O35">
-        <v>0.81106205</v>
+        <v>0.8085109</v>
       </c>
       <c r="P35">
-        <v>2.43318615</v>
+        <v>2.4255327</v>
       </c>
       <c r="Q35">
-        <v>2.66218615</v>
+        <v>2.6545327</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1233490504845779</v>
+        <v>0.1243095291876318</v>
       </c>
       <c r="T35">
-        <v>1.128433175194781</v>
+        <v>1.142409310631922</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.63394464409693</v>
+        <v>10.32118156632937</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.095253289263837</v>
+        <v>0.09504221470300683</v>
       </c>
       <c r="C36">
-        <v>13.85028748343974</v>
+        <v>13.6879168471231</v>
       </c>
       <c r="D36">
-        <v>19.99628748343974</v>
+        <v>20.0309168471231</v>
       </c>
       <c r="E36">
-        <v>1.698000000000001</v>
+        <v>1.895000000000001</v>
       </c>
       <c r="F36">
-        <v>6.698</v>
+        <v>6.895</v>
       </c>
       <c r="G36">
         <v>0.552</v>
@@ -4221,28 +4221,28 @@
         <v>3.581</v>
       </c>
       <c r="M36">
-        <v>0.3469564</v>
+        <v>0.357161</v>
       </c>
       <c r="N36">
-        <v>3.2340436</v>
+        <v>3.223839</v>
       </c>
       <c r="O36">
-        <v>0.8085109</v>
+        <v>0.80595975</v>
       </c>
       <c r="P36">
-        <v>2.4255327</v>
+        <v>2.41787925</v>
       </c>
       <c r="Q36">
-        <v>2.6545327</v>
+        <v>2.64687925</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1243095291876318</v>
+        <v>0.125299561081549</v>
       </c>
       <c r="T36">
-        <v>1.142409310631922</v>
+        <v>1.156815481005591</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.32118156632937</v>
+        <v>10.02629066443425</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09504221470300683</v>
+        <v>0.09529014014217668</v>
       </c>
       <c r="C37">
-        <v>13.6879168471231</v>
+        <v>13.45025391916826</v>
       </c>
       <c r="D37">
-        <v>20.0309168471231</v>
+        <v>19.99025391916826</v>
       </c>
       <c r="E37">
-        <v>1.895000000000001</v>
+        <v>2.092000000000001</v>
       </c>
       <c r="F37">
-        <v>6.895</v>
+        <v>7.092000000000001</v>
       </c>
       <c r="G37">
         <v>0.552</v>
@@ -4303,45 +4303,45 @@
         <v>3.581</v>
       </c>
       <c r="M37">
-        <v>0.357161</v>
+        <v>0.379422</v>
       </c>
       <c r="N37">
-        <v>3.223839</v>
+        <v>3.201578</v>
       </c>
       <c r="O37">
-        <v>0.80595975</v>
+        <v>0.8003945</v>
       </c>
       <c r="P37">
-        <v>2.41787925</v>
+        <v>2.4011835</v>
       </c>
       <c r="Q37">
-        <v>2.64687925</v>
+        <v>2.6301835</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.125299561081549</v>
+        <v>0.1263205314721511</v>
       </c>
       <c r="T37">
-        <v>1.156815481005591</v>
+        <v>1.171671844203437</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>10.02629066443425</v>
+        <v>9.438039966053628</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0952901401421767</v>
+        <v>0.09509181558134654</v>
       </c>
       <c r="C38">
-        <v>13.45025391916826</v>
+        <v>13.28576843967375</v>
       </c>
       <c r="D38">
-        <v>19.99025391916826</v>
+        <v>20.02276843967375</v>
       </c>
       <c r="E38">
-        <v>2.092000000000001</v>
+        <v>2.289000000000001</v>
       </c>
       <c r="F38">
-        <v>7.092</v>
+        <v>7.289</v>
       </c>
       <c r="G38">
         <v>0.552</v>
@@ -4385,28 +4385,28 @@
         <v>3.581</v>
       </c>
       <c r="M38">
-        <v>0.379422</v>
+        <v>0.3899615</v>
       </c>
       <c r="N38">
-        <v>3.201578</v>
+        <v>3.1910385</v>
       </c>
       <c r="O38">
-        <v>0.8003945</v>
+        <v>0.797759625</v>
       </c>
       <c r="P38">
-        <v>2.4011835</v>
+        <v>2.393278875</v>
       </c>
       <c r="Q38">
-        <v>2.6301835</v>
+        <v>2.622278875</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1263205314721511</v>
+        <v>0.127373913621185</v>
       </c>
       <c r="T38">
-        <v>1.171671844203437</v>
+        <v>1.186999837978992</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.43803996605363</v>
+        <v>9.182957804808936</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09509181558134654</v>
+        <v>0.09489349102051639</v>
       </c>
       <c r="C39">
-        <v>13.28576843967375</v>
+        <v>13.12138890344491</v>
       </c>
       <c r="D39">
-        <v>20.02276843967375</v>
+        <v>20.05538890344491</v>
       </c>
       <c r="E39">
-        <v>2.289000000000001</v>
+        <v>2.486000000000001</v>
       </c>
       <c r="F39">
-        <v>7.289</v>
+        <v>7.486</v>
       </c>
       <c r="G39">
         <v>0.552</v>
@@ -4467,28 +4467,28 @@
         <v>3.581</v>
       </c>
       <c r="M39">
-        <v>0.3899615</v>
+        <v>0.400501</v>
       </c>
       <c r="N39">
-        <v>3.1910385</v>
+        <v>3.180499</v>
       </c>
       <c r="O39">
-        <v>0.797759625</v>
+        <v>0.79512475</v>
       </c>
       <c r="P39">
-        <v>2.393278875</v>
+        <v>2.38537425</v>
       </c>
       <c r="Q39">
-        <v>2.622278875</v>
+        <v>2.61437425</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.127373913621185</v>
+        <v>0.1284612758395426</v>
       </c>
       <c r="T39">
-        <v>1.186999837978992</v>
+        <v>1.202822283166662</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.182957804808936</v>
+        <v>8.94130102047186</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09489349102051639</v>
+        <v>0.09469516645968623</v>
       </c>
       <c r="C40">
-        <v>13.12138890344491</v>
+        <v>12.95711582912501</v>
       </c>
       <c r="D40">
-        <v>20.05538890344491</v>
+        <v>20.08811582912501</v>
       </c>
       <c r="E40">
-        <v>2.486000000000001</v>
+        <v>2.683000000000001</v>
       </c>
       <c r="F40">
-        <v>7.486</v>
+        <v>7.683</v>
       </c>
       <c r="G40">
         <v>0.552</v>
@@ -4549,28 +4549,28 @@
         <v>3.581</v>
       </c>
       <c r="M40">
-        <v>0.400501</v>
+        <v>0.4110405</v>
       </c>
       <c r="N40">
-        <v>3.180499</v>
+        <v>3.1699595</v>
       </c>
       <c r="O40">
-        <v>0.79512475</v>
+        <v>0.792489875</v>
       </c>
       <c r="P40">
-        <v>2.38537425</v>
+        <v>2.377469625</v>
       </c>
       <c r="Q40">
-        <v>2.61437425</v>
+        <v>2.606469625</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1284612758395426</v>
+        <v>0.1295842892781741</v>
       </c>
       <c r="T40">
-        <v>1.202822283166662</v>
+        <v>1.219163497049009</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.94130102047186</v>
+        <v>8.712036891741812</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09469516645968623</v>
+        <v>0.09449684189885604</v>
       </c>
       <c r="C41">
-        <v>12.95711582912501</v>
+        <v>12.79294973874816</v>
       </c>
       <c r="D41">
-        <v>20.08811582912501</v>
+        <v>20.12094973874816</v>
       </c>
       <c r="E41">
-        <v>2.683000000000001</v>
+        <v>2.880000000000001</v>
       </c>
       <c r="F41">
-        <v>7.683</v>
+        <v>7.88</v>
       </c>
       <c r="G41">
         <v>0.552</v>
@@ -4631,28 +4631,28 @@
         <v>3.581</v>
       </c>
       <c r="M41">
-        <v>0.4110405</v>
+        <v>0.42158</v>
       </c>
       <c r="N41">
-        <v>3.1699595</v>
+        <v>3.15942</v>
       </c>
       <c r="O41">
-        <v>0.792489875</v>
+        <v>0.789855</v>
       </c>
       <c r="P41">
-        <v>2.377469625</v>
+        <v>2.369565</v>
       </c>
       <c r="Q41">
-        <v>2.606469625</v>
+        <v>2.598565</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1295842892781741</v>
+        <v>0.1307447364980934</v>
       </c>
       <c r="T41">
-        <v>1.219163497049009</v>
+        <v>1.236049418060768</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.712036891741812</v>
+        <v>8.494235969448265</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09449684189885604</v>
+        <v>0.09429851733802591</v>
       </c>
       <c r="C42">
-        <v>12.79294973874816</v>
+        <v>12.62889115776713</v>
       </c>
       <c r="D42">
-        <v>20.12094973874816</v>
+        <v>20.15389115776713</v>
       </c>
       <c r="E42">
-        <v>2.880000000000001</v>
+        <v>3.077000000000001</v>
       </c>
       <c r="F42">
-        <v>7.88</v>
+        <v>8.077</v>
       </c>
       <c r="G42">
         <v>0.552</v>
@@ -4713,28 +4713,28 @@
         <v>3.581</v>
       </c>
       <c r="M42">
-        <v>0.42158</v>
+        <v>0.4321195</v>
       </c>
       <c r="N42">
-        <v>3.15942</v>
+        <v>3.1488805</v>
       </c>
       <c r="O42">
-        <v>0.789855</v>
+        <v>0.7872201249999999</v>
       </c>
       <c r="P42">
-        <v>2.369565</v>
+        <v>2.361660375</v>
       </c>
       <c r="Q42">
-        <v>2.598565</v>
+        <v>2.590660375</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1307447364980934</v>
+        <v>0.1319445209119083</v>
       </c>
       <c r="T42">
-        <v>1.236049418060768</v>
+        <v>1.253507743174621</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.494235969448265</v>
+        <v>8.287059482388552</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09429851733802591</v>
+        <v>0.09410019277719575</v>
       </c>
       <c r="C43">
-        <v>12.62889115776713</v>
+        <v>12.46494061508137</v>
       </c>
       <c r="D43">
-        <v>20.15389115776713</v>
+        <v>20.18694061508137</v>
       </c>
       <c r="E43">
-        <v>3.077000000000001</v>
+        <v>3.274000000000002</v>
       </c>
       <c r="F43">
-        <v>8.077</v>
+        <v>8.274000000000001</v>
       </c>
       <c r="G43">
         <v>0.552</v>
@@ -4795,28 +4795,28 @@
         <v>3.581</v>
       </c>
       <c r="M43">
-        <v>0.4321195</v>
+        <v>0.442659</v>
       </c>
       <c r="N43">
-        <v>3.1488805</v>
+        <v>3.138341</v>
       </c>
       <c r="O43">
-        <v>0.7872201249999999</v>
+        <v>0.78458525</v>
       </c>
       <c r="P43">
-        <v>2.361660375</v>
+        <v>2.35375575</v>
       </c>
       <c r="Q43">
-        <v>2.590660375</v>
+        <v>2.58275575</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1319445209119083</v>
+        <v>0.1331856772020616</v>
       </c>
       <c r="T43">
-        <v>1.253507743174621</v>
+        <v>1.271568079499296</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.287059482388552</v>
+        <v>8.089748542331682</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09410019277719575</v>
+        <v>0.09390186821636559</v>
       </c>
       <c r="C44">
-        <v>12.46494061508137</v>
+        <v>12.30109864306527</v>
       </c>
       <c r="D44">
-        <v>20.18694061508137</v>
+        <v>20.22009864306527</v>
       </c>
       <c r="E44">
-        <v>3.274</v>
+        <v>3.471000000000001</v>
       </c>
       <c r="F44">
-        <v>8.273999999999999</v>
+        <v>8.471</v>
       </c>
       <c r="G44">
         <v>0.552</v>
@@ -4877,28 +4877,28 @@
         <v>3.581</v>
       </c>
       <c r="M44">
-        <v>0.442659</v>
+        <v>0.4531985</v>
       </c>
       <c r="N44">
-        <v>3.138341</v>
+        <v>3.1278015</v>
       </c>
       <c r="O44">
-        <v>0.78458525</v>
+        <v>0.781950375</v>
       </c>
       <c r="P44">
-        <v>2.35375575</v>
+        <v>2.345851125</v>
       </c>
       <c r="Q44">
-        <v>2.58275575</v>
+        <v>2.574851125</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1331856772020616</v>
+        <v>0.1344703828357291</v>
       </c>
       <c r="T44">
-        <v>1.271568079499296</v>
+        <v>1.290262111835363</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.089748542331684</v>
+        <v>7.901614855300712</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09390186821636559</v>
+        <v>0.09370354365553546</v>
       </c>
       <c r="C45">
-        <v>12.30109864306527</v>
+        <v>12.13736577759677</v>
       </c>
       <c r="D45">
-        <v>20.22009864306527</v>
+        <v>20.25336577759677</v>
       </c>
       <c r="E45">
-        <v>3.471000000000001</v>
+        <v>3.668</v>
       </c>
       <c r="F45">
-        <v>8.471</v>
+        <v>8.667999999999999</v>
       </c>
       <c r="G45">
         <v>0.552</v>
@@ -4959,28 +4959,28 @@
         <v>3.581</v>
       </c>
       <c r="M45">
-        <v>0.4531985</v>
+        <v>0.4637379999999999</v>
       </c>
       <c r="N45">
-        <v>3.1278015</v>
+        <v>3.117262</v>
       </c>
       <c r="O45">
-        <v>0.781950375</v>
+        <v>0.7793155</v>
       </c>
       <c r="P45">
-        <v>2.345851125</v>
+        <v>2.3379465</v>
       </c>
       <c r="Q45">
-        <v>2.574851125</v>
+        <v>2.5669465</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1344703828357291</v>
+        <v>0.1358009708134562</v>
       </c>
       <c r="T45">
-        <v>1.290262111835363</v>
+        <v>1.309623788183433</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.901614855300712</v>
+        <v>7.722032699498425</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09370354365553546</v>
+        <v>0.09377521909470529</v>
       </c>
       <c r="C46">
-        <v>12.13736577759677</v>
+        <v>11.9283302526701</v>
       </c>
       <c r="D46">
-        <v>20.25336577759677</v>
+        <v>20.2413302526701</v>
       </c>
       <c r="E46">
-        <v>3.668</v>
+        <v>3.865000000000001</v>
       </c>
       <c r="F46">
-        <v>8.667999999999999</v>
+        <v>8.865</v>
       </c>
       <c r="G46">
         <v>0.552</v>
@@ -5041,45 +5041,45 @@
         <v>3.581</v>
       </c>
       <c r="M46">
-        <v>0.4637379999999999</v>
+        <v>0.4813695</v>
       </c>
       <c r="N46">
-        <v>3.117262</v>
+        <v>3.0996305</v>
       </c>
       <c r="O46">
-        <v>0.7793155</v>
+        <v>0.774907625</v>
       </c>
       <c r="P46">
-        <v>2.3379465</v>
+        <v>2.324722875</v>
       </c>
       <c r="Q46">
-        <v>2.5669465</v>
+        <v>2.553722875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1358009708134562</v>
+        <v>0.1371799438085551</v>
       </c>
       <c r="T46">
-        <v>1.309623788183433</v>
+        <v>1.329689525489614</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.722032699498425</v>
+        <v>7.439191722782603</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09377521909470529</v>
+        <v>0.09358289453387512</v>
       </c>
       <c r="C47">
-        <v>11.9283302526701</v>
+        <v>11.76365717170914</v>
       </c>
       <c r="D47">
-        <v>20.2413302526701</v>
+        <v>20.27365717170914</v>
       </c>
       <c r="E47">
-        <v>3.865000000000001</v>
+        <v>4.062</v>
       </c>
       <c r="F47">
-        <v>8.865</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="G47">
         <v>0.552</v>
@@ -5123,28 +5123,28 @@
         <v>3.581</v>
       </c>
       <c r="M47">
-        <v>0.4813695</v>
+        <v>0.4920666</v>
       </c>
       <c r="N47">
-        <v>3.0996305</v>
+        <v>3.0889334</v>
       </c>
       <c r="O47">
-        <v>0.774907625</v>
+        <v>0.77223335</v>
       </c>
       <c r="P47">
-        <v>2.324722875</v>
+        <v>2.31670005</v>
       </c>
       <c r="Q47">
-        <v>2.553722875</v>
+        <v>2.54570005</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1371799438085551</v>
+        <v>0.1386099898775465</v>
       </c>
       <c r="T47">
-        <v>1.329689525489614</v>
+        <v>1.35049843825158</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.439191722782603</v>
+        <v>7.277470163591677</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09358289453387512</v>
+        <v>0.09339056997304497</v>
       </c>
       <c r="C48">
-        <v>11.76365717170914</v>
+        <v>11.5990875129385</v>
       </c>
       <c r="D48">
-        <v>20.27365717170914</v>
+        <v>20.3060875129385</v>
       </c>
       <c r="E48">
-        <v>4.062</v>
+        <v>4.259000000000001</v>
       </c>
       <c r="F48">
-        <v>9.061999999999999</v>
+        <v>9.259</v>
       </c>
       <c r="G48">
         <v>0.552</v>
@@ -5205,28 +5205,28 @@
         <v>3.581</v>
       </c>
       <c r="M48">
-        <v>0.4920666</v>
+        <v>0.5027637</v>
       </c>
       <c r="N48">
-        <v>3.0889334</v>
+        <v>3.0782363</v>
       </c>
       <c r="O48">
-        <v>0.77223335</v>
+        <v>0.769559075</v>
       </c>
       <c r="P48">
-        <v>2.31670005</v>
+        <v>2.308677225</v>
       </c>
       <c r="Q48">
-        <v>2.54570005</v>
+        <v>2.537677225</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1386099898775465</v>
+        <v>0.1400939999491415</v>
       </c>
       <c r="T48">
-        <v>1.35049843825158</v>
+        <v>1.372092593004564</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.277470163591677</v>
+        <v>7.12263037287696</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09339056997304497</v>
+        <v>0.0931982454122148</v>
       </c>
       <c r="C49">
-        <v>11.5990875129385</v>
+        <v>11.43462177346495</v>
       </c>
       <c r="D49">
-        <v>20.3060875129385</v>
+        <v>20.33862177346495</v>
       </c>
       <c r="E49">
-        <v>4.259000000000001</v>
+        <v>4.456</v>
       </c>
       <c r="F49">
-        <v>9.259</v>
+        <v>9.456</v>
       </c>
       <c r="G49">
         <v>0.552</v>
@@ -5287,28 +5287,28 @@
         <v>3.581</v>
       </c>
       <c r="M49">
-        <v>0.5027637</v>
+        <v>0.5134607999999999</v>
       </c>
       <c r="N49">
-        <v>3.0782363</v>
+        <v>3.0675392</v>
       </c>
       <c r="O49">
-        <v>0.769559075</v>
+        <v>0.7668848</v>
       </c>
       <c r="P49">
-        <v>2.308677225</v>
+        <v>2.3006544</v>
       </c>
       <c r="Q49">
-        <v>2.537677225</v>
+        <v>2.5296544</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1400939999491415</v>
+        <v>0.1416350873311823</v>
       </c>
       <c r="T49">
-        <v>1.372092593004564</v>
+        <v>1.394517292171123</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.12263037287696</v>
+        <v>6.974242240108691</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0931982454122148</v>
+        <v>0.09300592085138465</v>
       </c>
       <c r="C50">
-        <v>11.43462177346495</v>
+        <v>11.27026045358622</v>
       </c>
       <c r="D50">
-        <v>20.33862177346495</v>
+        <v>20.37126045358622</v>
       </c>
       <c r="E50">
-        <v>4.456</v>
+        <v>4.653</v>
       </c>
       <c r="F50">
-        <v>9.456</v>
+        <v>9.652999999999999</v>
       </c>
       <c r="G50">
         <v>0.552</v>
@@ -5369,28 +5369,28 @@
         <v>3.581</v>
       </c>
       <c r="M50">
-        <v>0.5134607999999999</v>
+        <v>0.5241579</v>
       </c>
       <c r="N50">
-        <v>3.0675392</v>
+        <v>3.0568421</v>
       </c>
       <c r="O50">
-        <v>0.7668848</v>
+        <v>0.764210525</v>
       </c>
       <c r="P50">
-        <v>2.3006544</v>
+        <v>2.292631575</v>
       </c>
       <c r="Q50">
-        <v>2.5296544</v>
+        <v>2.521631575</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1416350873311823</v>
+        <v>0.1432366095125189</v>
       </c>
       <c r="T50">
-        <v>1.394517292171123</v>
+        <v>1.417821391304999</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.974242240108691</v>
+        <v>6.831910765820758</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09300592085138465</v>
+        <v>0.0928135962905545</v>
       </c>
       <c r="C51">
-        <v>11.27026045358622</v>
+        <v>11.10600405681661</v>
       </c>
       <c r="D51">
-        <v>20.37126045358622</v>
+        <v>20.40400405681661</v>
       </c>
       <c r="E51">
-        <v>4.653</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="F51">
-        <v>9.652999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="G51">
         <v>0.552</v>
@@ -5451,28 +5451,28 @@
         <v>3.581</v>
       </c>
       <c r="M51">
-        <v>0.5241579</v>
+        <v>0.534855</v>
       </c>
       <c r="N51">
-        <v>3.0568421</v>
+        <v>3.046145</v>
       </c>
       <c r="O51">
-        <v>0.764210525</v>
+        <v>0.76153625</v>
       </c>
       <c r="P51">
-        <v>2.292631575</v>
+        <v>2.28460875</v>
       </c>
       <c r="Q51">
-        <v>2.521631575</v>
+        <v>2.51360875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1432366095125189</v>
+        <v>0.144902192581109</v>
       </c>
       <c r="T51">
-        <v>1.417821391304999</v>
+        <v>1.44205765440423</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.831910765820758</v>
+        <v>6.695272550504343</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0928135962905545</v>
+        <v>0.09262127172972436</v>
       </c>
       <c r="C52">
-        <v>11.10600405681661</v>
+        <v>10.94185308991295</v>
       </c>
       <c r="D52">
-        <v>20.40400405681661</v>
+        <v>20.43685308991295</v>
       </c>
       <c r="E52">
-        <v>4.850000000000001</v>
+        <v>5.047000000000001</v>
       </c>
       <c r="F52">
-        <v>9.85</v>
+        <v>10.047</v>
       </c>
       <c r="G52">
         <v>0.552</v>
@@ -5533,28 +5533,28 @@
         <v>3.581</v>
       </c>
       <c r="M52">
-        <v>0.534855</v>
+        <v>0.5455521000000001</v>
       </c>
       <c r="N52">
-        <v>3.046145</v>
+        <v>3.0354479</v>
       </c>
       <c r="O52">
-        <v>0.76153625</v>
+        <v>0.758861975</v>
       </c>
       <c r="P52">
-        <v>2.28460875</v>
+        <v>2.276585925</v>
       </c>
       <c r="Q52">
-        <v>2.51360875</v>
+        <v>2.505585925</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.144902192581109</v>
+        <v>0.1466357586320905</v>
       </c>
       <c r="T52">
-        <v>1.44205765440423</v>
+        <v>1.467283152732</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.695272550504343</v>
+        <v>6.563992696572884</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09262127172972436</v>
+        <v>0.0924289471688942</v>
       </c>
       <c r="C53">
-        <v>10.94185308991295</v>
+        <v>10.77780806290068</v>
       </c>
       <c r="D53">
-        <v>20.43685308991295</v>
+        <v>20.46980806290068</v>
       </c>
       <c r="E53">
-        <v>5.047000000000001</v>
+        <v>5.244000000000001</v>
       </c>
       <c r="F53">
-        <v>10.047</v>
+        <v>10.244</v>
       </c>
       <c r="G53">
         <v>0.552</v>
@@ -5615,28 +5615,28 @@
         <v>3.581</v>
       </c>
       <c r="M53">
-        <v>0.5455521000000001</v>
+        <v>0.5562492</v>
       </c>
       <c r="N53">
-        <v>3.0354479</v>
+        <v>3.0247508</v>
       </c>
       <c r="O53">
-        <v>0.758861975</v>
+        <v>0.7561877</v>
       </c>
       <c r="P53">
-        <v>2.276585925</v>
+        <v>2.2685631</v>
       </c>
       <c r="Q53">
-        <v>2.505585925</v>
+        <v>2.4975631</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1466357586320905</v>
+        <v>0.1484415566018629</v>
       </c>
       <c r="T53">
-        <v>1.467283152732</v>
+        <v>1.493559713490095</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.563992696572884</v>
+        <v>6.437762067792637</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0924289471688942</v>
+        <v>0.09223662260806403</v>
       </c>
       <c r="C54">
-        <v>10.77780806290068</v>
+        <v>10.61386948910028</v>
       </c>
       <c r="D54">
-        <v>20.46980806290068</v>
+        <v>20.50286948910028</v>
       </c>
       <c r="E54">
-        <v>5.244000000000001</v>
+        <v>5.441000000000002</v>
       </c>
       <c r="F54">
-        <v>10.244</v>
+        <v>10.441</v>
       </c>
       <c r="G54">
         <v>0.552</v>
@@ -5697,28 +5697,28 @@
         <v>3.581</v>
       </c>
       <c r="M54">
-        <v>0.5562492</v>
+        <v>0.5669463</v>
       </c>
       <c r="N54">
-        <v>3.0247508</v>
+        <v>3.0140537</v>
       </c>
       <c r="O54">
-        <v>0.7561877</v>
+        <v>0.753513425</v>
       </c>
       <c r="P54">
-        <v>2.2685631</v>
+        <v>2.260540275</v>
       </c>
       <c r="Q54">
-        <v>2.4975631</v>
+        <v>2.489540275</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1484415566018629</v>
+        <v>0.1503241970384341</v>
       </c>
       <c r="T54">
-        <v>1.493559713490095</v>
+        <v>1.520954425769811</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.437762067792637</v>
+        <v>6.31629485896636</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09223662260806403</v>
+        <v>0.09204429804723388</v>
       </c>
       <c r="C55">
-        <v>10.61386948910028</v>
+        <v>10.45003788515392</v>
       </c>
       <c r="D55">
-        <v>20.50286948910028</v>
+        <v>20.53603788515392</v>
       </c>
       <c r="E55">
-        <v>5.441000000000002</v>
+        <v>5.638000000000001</v>
       </c>
       <c r="F55">
-        <v>10.441</v>
+        <v>10.638</v>
       </c>
       <c r="G55">
         <v>0.552</v>
@@ -5779,28 +5779,28 @@
         <v>3.581</v>
       </c>
       <c r="M55">
-        <v>0.5669463</v>
+        <v>0.5776434</v>
       </c>
       <c r="N55">
-        <v>3.0140537</v>
+        <v>3.0033566</v>
       </c>
       <c r="O55">
-        <v>0.753513425</v>
+        <v>0.75083915</v>
       </c>
       <c r="P55">
-        <v>2.260540275</v>
+        <v>2.25251745</v>
       </c>
       <c r="Q55">
-        <v>2.489540275</v>
+        <v>2.48151745</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1503241970384341</v>
+        <v>0.1522886914070302</v>
       </c>
       <c r="T55">
-        <v>1.520954425769811</v>
+        <v>1.549540212496471</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.31629485896636</v>
+        <v>6.199326435652169</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09204429804723388</v>
+        <v>0.09226447348640374</v>
       </c>
       <c r="C56">
-        <v>10.45003788515392</v>
+        <v>10.21507519090942</v>
       </c>
       <c r="D56">
-        <v>20.53603788515392</v>
+        <v>20.49807519090942</v>
       </c>
       <c r="E56">
-        <v>5.638000000000001</v>
+        <v>5.835000000000002</v>
       </c>
       <c r="F56">
-        <v>10.638</v>
+        <v>10.835</v>
       </c>
       <c r="G56">
         <v>0.552</v>
@@ -5861,45 +5861,45 @@
         <v>3.581</v>
       </c>
       <c r="M56">
-        <v>0.5776434</v>
+        <v>0.5991755000000001</v>
       </c>
       <c r="N56">
-        <v>3.0033566</v>
+        <v>2.9818245</v>
       </c>
       <c r="O56">
-        <v>0.75083915</v>
+        <v>0.745456125</v>
       </c>
       <c r="P56">
-        <v>2.25251745</v>
+        <v>2.236368375</v>
       </c>
       <c r="Q56">
-        <v>2.48151745</v>
+        <v>2.465368375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1522886914070302</v>
+        <v>0.1543404966364527</v>
       </c>
       <c r="T56">
-        <v>1.549540212496471</v>
+        <v>1.579396478633204</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.199326435652169</v>
+        <v>5.976546103770931</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09226447348640374</v>
+        <v>0.09207964892557356</v>
       </c>
       <c r="C57">
-        <v>10.21507519090942</v>
+        <v>10.04993320634083</v>
       </c>
       <c r="D57">
-        <v>20.49807519090942</v>
+        <v>20.52993320634083</v>
       </c>
       <c r="E57">
-        <v>5.835000000000002</v>
+        <v>6.032000000000001</v>
       </c>
       <c r="F57">
-        <v>10.835</v>
+        <v>11.032</v>
       </c>
       <c r="G57">
         <v>0.552</v>
@@ -5943,28 +5943,28 @@
         <v>3.581</v>
       </c>
       <c r="M57">
-        <v>0.5991755000000001</v>
+        <v>0.6100696</v>
       </c>
       <c r="N57">
-        <v>2.9818245</v>
+        <v>2.9709304</v>
       </c>
       <c r="O57">
-        <v>0.745456125</v>
+        <v>0.7427326</v>
       </c>
       <c r="P57">
-        <v>2.236368375</v>
+        <v>2.2281978</v>
       </c>
       <c r="Q57">
-        <v>2.465368375</v>
+        <v>2.4571978</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1543404966364527</v>
+        <v>0.1564855657399399</v>
       </c>
       <c r="T57">
-        <v>1.579396478633204</v>
+        <v>1.610609847776153</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.976546103770931</v>
+        <v>5.869822066203594</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09207964892557356</v>
+        <v>0.09189482436474342</v>
       </c>
       <c r="C58">
-        <v>10.04993320634083</v>
+        <v>9.884890403085373</v>
       </c>
       <c r="D58">
-        <v>20.52993320634083</v>
+        <v>20.56189040308537</v>
       </c>
       <c r="E58">
-        <v>6.032000000000001</v>
+        <v>6.229000000000002</v>
       </c>
       <c r="F58">
-        <v>11.032</v>
+        <v>11.229</v>
       </c>
       <c r="G58">
         <v>0.552</v>
@@ -6025,28 +6025,28 @@
         <v>3.581</v>
       </c>
       <c r="M58">
-        <v>0.6100696</v>
+        <v>0.6209637000000001</v>
       </c>
       <c r="N58">
-        <v>2.9709304</v>
+        <v>2.9600363</v>
       </c>
       <c r="O58">
-        <v>0.7427326</v>
+        <v>0.7400090749999999</v>
       </c>
       <c r="P58">
-        <v>2.2281978</v>
+        <v>2.220027225</v>
       </c>
       <c r="Q58">
-        <v>2.4571978</v>
+        <v>2.449027225</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1564855657399399</v>
+        <v>0.1587304054994033</v>
       </c>
       <c r="T58">
-        <v>1.610609847776153</v>
+        <v>1.643275001530401</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.869822066203594</v>
+        <v>5.766842731708793</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09189482436474342</v>
+        <v>0.09170999980391326</v>
       </c>
       <c r="C59">
-        <v>9.884890403085373</v>
+        <v>9.719947245026434</v>
       </c>
       <c r="D59">
-        <v>20.56189040308537</v>
+        <v>20.59394724502643</v>
       </c>
       <c r="E59">
-        <v>6.229000000000002</v>
+        <v>6.426000000000001</v>
       </c>
       <c r="F59">
-        <v>11.229</v>
+        <v>11.426</v>
       </c>
       <c r="G59">
         <v>0.552</v>
@@ -6107,28 +6107,28 @@
         <v>3.581</v>
       </c>
       <c r="M59">
-        <v>0.6209637000000001</v>
+        <v>0.6318578</v>
       </c>
       <c r="N59">
-        <v>2.9600363</v>
+        <v>2.9491422</v>
       </c>
       <c r="O59">
-        <v>0.7400090749999999</v>
+        <v>0.73728555</v>
       </c>
       <c r="P59">
-        <v>2.220027225</v>
+        <v>2.21185665</v>
       </c>
       <c r="Q59">
-        <v>2.449027225</v>
+        <v>2.44085665</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1587304054994033</v>
+        <v>0.1610821423902697</v>
       </c>
       <c r="T59">
-        <v>1.643275001530401</v>
+        <v>1.677495638796757</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.766842731708793</v>
+        <v>5.667414408748297</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09170999980391326</v>
+        <v>0.09152517524308311</v>
       </c>
       <c r="C60">
-        <v>9.719947245026436</v>
+        <v>9.555104198944745</v>
       </c>
       <c r="D60">
-        <v>20.59394724502643</v>
+        <v>20.62610419894474</v>
       </c>
       <c r="E60">
-        <v>6.425999999999999</v>
+        <v>6.623</v>
       </c>
       <c r="F60">
-        <v>11.426</v>
+        <v>11.623</v>
       </c>
       <c r="G60">
         <v>0.552</v>
@@ -6189,28 +6189,28 @@
         <v>3.581</v>
       </c>
       <c r="M60">
-        <v>0.6318577999999999</v>
+        <v>0.6427518999999999</v>
       </c>
       <c r="N60">
-        <v>2.9491422</v>
+        <v>2.9382481</v>
       </c>
       <c r="O60">
-        <v>0.73728555</v>
+        <v>0.734562025</v>
       </c>
       <c r="P60">
-        <v>2.21185665</v>
+        <v>2.203686075</v>
       </c>
       <c r="Q60">
-        <v>2.44085665</v>
+        <v>2.432686075</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1610821423902697</v>
+        <v>0.1635485981538612</v>
       </c>
       <c r="T60">
-        <v>1.677495638796757</v>
+        <v>1.713385575441959</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.667414408748298</v>
+        <v>5.571356537413581</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09152517524308311</v>
+        <v>0.09134035068225296</v>
       </c>
       <c r="C61">
-        <v>9.555104198944745</v>
+        <v>9.390361734541075</v>
       </c>
       <c r="D61">
-        <v>20.62610419894474</v>
+        <v>20.65836173454107</v>
       </c>
       <c r="E61">
-        <v>6.623</v>
+        <v>6.819999999999999</v>
       </c>
       <c r="F61">
-        <v>11.623</v>
+        <v>11.82</v>
       </c>
       <c r="G61">
         <v>0.552</v>
@@ -6271,28 +6271,28 @@
         <v>3.581</v>
       </c>
       <c r="M61">
-        <v>0.6427518999999999</v>
+        <v>0.6536459999999999</v>
       </c>
       <c r="N61">
-        <v>2.9382481</v>
+        <v>2.927354</v>
       </c>
       <c r="O61">
-        <v>0.734562025</v>
+        <v>0.7318385000000001</v>
       </c>
       <c r="P61">
-        <v>2.203686075</v>
+        <v>2.1955155</v>
       </c>
       <c r="Q61">
-        <v>2.432686075</v>
+        <v>2.4245155</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1635485981538612</v>
+        <v>0.1661383767056324</v>
       </c>
       <c r="T61">
-        <v>1.713385575441959</v>
+        <v>1.751070008919422</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.571356537413581</v>
+        <v>5.478500595123355</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09134035068225296</v>
+        <v>0.09115552612142279</v>
       </c>
       <c r="C62">
-        <v>9.390361734541075</v>
+        <v>9.225720324459097</v>
       </c>
       <c r="D62">
-        <v>20.65836173454107</v>
+        <v>20.6907203244591</v>
       </c>
       <c r="E62">
-        <v>6.819999999999999</v>
+        <v>7.017</v>
       </c>
       <c r="F62">
-        <v>11.82</v>
+        <v>12.017</v>
       </c>
       <c r="G62">
         <v>0.552</v>
@@ -6353,28 +6353,28 @@
         <v>3.581</v>
       </c>
       <c r="M62">
-        <v>0.6536459999999999</v>
+        <v>0.6645401</v>
       </c>
       <c r="N62">
-        <v>2.927354</v>
+        <v>2.9164599</v>
       </c>
       <c r="O62">
-        <v>0.7318385000000001</v>
+        <v>0.729114975</v>
       </c>
       <c r="P62">
-        <v>2.1955155</v>
+        <v>2.187344925</v>
       </c>
       <c r="Q62">
-        <v>2.4245155</v>
+        <v>2.416344925</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1661383767056324</v>
+        <v>0.1688609644139046</v>
       </c>
       <c r="T62">
-        <v>1.751070008919422</v>
+        <v>1.790686977447011</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.478500595123355</v>
+        <v>5.388689109957398</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09115552612142279</v>
+        <v>0.09097070156059264</v>
       </c>
       <c r="C63">
-        <v>9.225720324459097</v>
+        <v>9.061180444308452</v>
       </c>
       <c r="D63">
-        <v>20.6907203244591</v>
+        <v>20.72318044430845</v>
       </c>
       <c r="E63">
-        <v>7.017</v>
+        <v>7.214</v>
       </c>
       <c r="F63">
-        <v>12.017</v>
+        <v>12.214</v>
       </c>
       <c r="G63">
         <v>0.552</v>
@@ -6435,28 +6435,28 @@
         <v>3.581</v>
       </c>
       <c r="M63">
-        <v>0.6645401</v>
+        <v>0.6754342</v>
       </c>
       <c r="N63">
-        <v>2.9164599</v>
+        <v>2.9055658</v>
       </c>
       <c r="O63">
-        <v>0.729114975</v>
+        <v>0.7263914499999999</v>
       </c>
       <c r="P63">
-        <v>2.187344925</v>
+        <v>2.17917435</v>
       </c>
       <c r="Q63">
-        <v>2.416344925</v>
+        <v>2.40817435</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1688609644139046</v>
+        <v>0.1717268462120859</v>
       </c>
       <c r="T63">
-        <v>1.790686977447011</v>
+        <v>1.832389049581314</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.388689109957398</v>
+        <v>5.301774769474213</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09097070156059264</v>
+        <v>0.09078587699976248</v>
       </c>
       <c r="C64">
-        <v>9.061180444308452</v>
+        <v>8.896742572688071</v>
       </c>
       <c r="D64">
-        <v>20.72318044430845</v>
+        <v>20.75574257268807</v>
       </c>
       <c r="E64">
-        <v>7.214</v>
+        <v>7.411</v>
       </c>
       <c r="F64">
-        <v>12.214</v>
+        <v>12.411</v>
       </c>
       <c r="G64">
         <v>0.552</v>
@@ -6517,28 +6517,28 @@
         <v>3.581</v>
       </c>
       <c r="M64">
-        <v>0.6754342</v>
+        <v>0.6863283</v>
       </c>
       <c r="N64">
-        <v>2.9055658</v>
+        <v>2.8946717</v>
       </c>
       <c r="O64">
-        <v>0.7263914499999999</v>
+        <v>0.723667925</v>
       </c>
       <c r="P64">
-        <v>2.17917435</v>
+        <v>2.171003775</v>
       </c>
       <c r="Q64">
-        <v>2.40817435</v>
+        <v>2.400003775</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1717268462120859</v>
+        <v>0.1747476405398986</v>
       </c>
       <c r="T64">
-        <v>1.832389049581314</v>
+        <v>1.876345287776932</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.301774769474213</v>
+        <v>5.217619614403194</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09078587699976248</v>
+        <v>0.09060105243893232</v>
       </c>
       <c r="C65">
-        <v>8.896742572688071</v>
+        <v>8.732407191209685</v>
       </c>
       <c r="D65">
-        <v>20.75574257268807</v>
+        <v>20.78840719120969</v>
       </c>
       <c r="E65">
-        <v>7.411</v>
+        <v>7.608000000000001</v>
       </c>
       <c r="F65">
-        <v>12.411</v>
+        <v>12.608</v>
       </c>
       <c r="G65">
         <v>0.552</v>
@@ -6599,28 +6599,28 @@
         <v>3.581</v>
       </c>
       <c r="M65">
-        <v>0.6863283</v>
+        <v>0.6972224</v>
       </c>
       <c r="N65">
-        <v>2.8946717</v>
+        <v>2.8837776</v>
       </c>
       <c r="O65">
-        <v>0.723667925</v>
+        <v>0.7209444</v>
       </c>
       <c r="P65">
-        <v>2.171003775</v>
+        <v>2.1628332</v>
       </c>
       <c r="Q65">
-        <v>2.400003775</v>
+        <v>2.3918332</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1747476405398986</v>
+        <v>0.177936256774812</v>
       </c>
       <c r="T65">
-        <v>1.876345287776932</v>
+        <v>1.92274353920564</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.217619614403194</v>
+        <v>5.136094307928145</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09060105243893232</v>
+        <v>0.09041622787810218</v>
       </c>
       <c r="C66">
-        <v>8.732407191209685</v>
+        <v>8.568174784521581</v>
       </c>
       <c r="D66">
-        <v>20.78840719120969</v>
+        <v>20.82117478452158</v>
       </c>
       <c r="E66">
-        <v>7.608000000000001</v>
+        <v>7.805000000000001</v>
       </c>
       <c r="F66">
-        <v>12.608</v>
+        <v>12.805</v>
       </c>
       <c r="G66">
         <v>0.552</v>
@@ -6681,28 +6681,28 @@
         <v>3.581</v>
       </c>
       <c r="M66">
-        <v>0.6972224</v>
+        <v>0.7081165</v>
       </c>
       <c r="N66">
-        <v>2.8837776</v>
+        <v>2.8728835</v>
       </c>
       <c r="O66">
-        <v>0.7209444</v>
+        <v>0.718220875</v>
       </c>
       <c r="P66">
-        <v>2.1628332</v>
+        <v>2.154662625</v>
       </c>
       <c r="Q66">
-        <v>2.3918332</v>
+        <v>2.383662625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.177936256774812</v>
+        <v>0.1813070796517205</v>
       </c>
       <c r="T66">
-        <v>1.92274353920564</v>
+        <v>1.971793119287416</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.136094307928145</v>
+        <v>5.057077472421557</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09041622787810218</v>
+        <v>0.090231403317272</v>
       </c>
       <c r="C67">
-        <v>8.568174784521581</v>
+        <v>8.404045840332563</v>
       </c>
       <c r="D67">
-        <v>20.82117478452158</v>
+        <v>20.85404584033256</v>
       </c>
       <c r="E67">
-        <v>7.805000000000001</v>
+        <v>8.002000000000002</v>
       </c>
       <c r="F67">
-        <v>12.805</v>
+        <v>13.002</v>
       </c>
       <c r="G67">
         <v>0.552</v>
@@ -6763,28 +6763,28 @@
         <v>3.581</v>
       </c>
       <c r="M67">
-        <v>0.7081165</v>
+        <v>0.7190106000000001</v>
       </c>
       <c r="N67">
-        <v>2.8728835</v>
+        <v>2.8619894</v>
       </c>
       <c r="O67">
-        <v>0.718220875</v>
+        <v>0.7154973499999999</v>
       </c>
       <c r="P67">
-        <v>2.154662625</v>
+        <v>2.14649205</v>
       </c>
       <c r="Q67">
-        <v>2.383662625</v>
+        <v>2.37549205</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1813070796517205</v>
+        <v>0.1848761862272706</v>
       </c>
       <c r="T67">
-        <v>1.971793119287416</v>
+        <v>2.023727968785768</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.057077472421557</v>
+        <v>4.980455086475776</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.090231403317272</v>
+        <v>0.09004657875644187</v>
       </c>
       <c r="C68">
-        <v>8.404045840332563</v>
+        <v>8.240020849436148</v>
       </c>
       <c r="D68">
-        <v>20.85404584033256</v>
+        <v>20.88702084943615</v>
       </c>
       <c r="E68">
-        <v>8.002000000000002</v>
+        <v>8.199000000000002</v>
       </c>
       <c r="F68">
-        <v>13.002</v>
+        <v>13.199</v>
       </c>
       <c r="G68">
         <v>0.552</v>
@@ -6845,28 +6845,28 @@
         <v>3.581</v>
       </c>
       <c r="M68">
-        <v>0.7190106000000001</v>
+        <v>0.7299047</v>
       </c>
       <c r="N68">
-        <v>2.8619894</v>
+        <v>2.8510953</v>
       </c>
       <c r="O68">
-        <v>0.7154973499999999</v>
+        <v>0.712773825</v>
       </c>
       <c r="P68">
-        <v>2.14649205</v>
+        <v>2.138321475</v>
       </c>
       <c r="Q68">
-        <v>2.37549205</v>
+        <v>2.367321475</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1848761862272706</v>
+        <v>0.1886616022922481</v>
       </c>
       <c r="T68">
-        <v>2.023727968785768</v>
+        <v>2.078810384920383</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.980455086475776</v>
+        <v>4.906119935931362</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09004657875644187</v>
+        <v>0.08986175419561171</v>
       </c>
       <c r="C69">
-        <v>8.240020849436148</v>
+        <v>8.076100305735</v>
       </c>
       <c r="D69">
-        <v>20.88702084943615</v>
+        <v>20.920100305735</v>
       </c>
       <c r="E69">
-        <v>8.199000000000002</v>
+        <v>8.396000000000001</v>
       </c>
       <c r="F69">
-        <v>13.199</v>
+        <v>13.396</v>
       </c>
       <c r="G69">
         <v>0.552</v>
@@ -6927,28 +6927,28 @@
         <v>3.581</v>
       </c>
       <c r="M69">
-        <v>0.7299047</v>
+        <v>0.7407988000000001</v>
       </c>
       <c r="N69">
-        <v>2.8510953</v>
+        <v>2.8402012</v>
       </c>
       <c r="O69">
-        <v>0.712773825</v>
+        <v>0.7100503</v>
       </c>
       <c r="P69">
-        <v>2.138321475</v>
+        <v>2.1301509</v>
       </c>
       <c r="Q69">
-        <v>2.367321475</v>
+        <v>2.3591509</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1886616022922481</v>
+        <v>0.1926836068612866</v>
       </c>
       <c r="T69">
-        <v>2.078810384920383</v>
+        <v>2.137335452063412</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.906119935931362</v>
+        <v>4.833971113344136</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08986175419561171</v>
+        <v>0.08967692963478155</v>
       </c>
       <c r="C70">
-        <v>8.076100305735</v>
+        <v>7.912284706265584</v>
       </c>
       <c r="D70">
-        <v>20.920100305735</v>
+        <v>20.95328470626558</v>
       </c>
       <c r="E70">
-        <v>8.396000000000001</v>
+        <v>8.593</v>
       </c>
       <c r="F70">
-        <v>13.396</v>
+        <v>13.593</v>
       </c>
       <c r="G70">
         <v>0.552</v>
@@ -7009,28 +7009,28 @@
         <v>3.581</v>
       </c>
       <c r="M70">
-        <v>0.7407988000000001</v>
+        <v>0.7516929</v>
       </c>
       <c r="N70">
-        <v>2.8402012</v>
+        <v>2.8293071</v>
       </c>
       <c r="O70">
-        <v>0.7100503</v>
+        <v>0.707326775</v>
       </c>
       <c r="P70">
-        <v>2.1301509</v>
+        <v>2.121980325</v>
       </c>
       <c r="Q70">
-        <v>2.3591509</v>
+        <v>2.350980325</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1926836068612866</v>
+        <v>0.1969650955960696</v>
       </c>
       <c r="T70">
-        <v>2.137335452063412</v>
+        <v>2.199636329989862</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.833971113344136</v>
+        <v>4.76391356097683</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08967692963478155</v>
+        <v>0.08949210507395139</v>
       </c>
       <c r="C71">
-        <v>7.912284706265584</v>
+        <v>7.748574551223056</v>
       </c>
       <c r="D71">
-        <v>20.95328470626558</v>
+        <v>20.98657455122306</v>
       </c>
       <c r="E71">
-        <v>8.593</v>
+        <v>8.790000000000003</v>
       </c>
       <c r="F71">
-        <v>13.593</v>
+        <v>13.79</v>
       </c>
       <c r="G71">
         <v>0.552</v>
@@ -7091,28 +7091,28 @@
         <v>3.581</v>
       </c>
       <c r="M71">
-        <v>0.7516929</v>
+        <v>0.7625870000000001</v>
       </c>
       <c r="N71">
-        <v>2.8293071</v>
+        <v>2.818413</v>
       </c>
       <c r="O71">
-        <v>0.707326775</v>
+        <v>0.7046032499999999</v>
       </c>
       <c r="P71">
-        <v>2.121980325</v>
+        <v>2.11380975</v>
       </c>
       <c r="Q71">
-        <v>2.350980325</v>
+        <v>2.34280975</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1969650955960696</v>
+        <v>0.2015320169131713</v>
       </c>
       <c r="T71">
-        <v>2.199636329989862</v>
+        <v>2.266090599778075</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.76391356097683</v>
+        <v>4.695857652962873</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08949210507395139</v>
+        <v>0.08930728051312123</v>
       </c>
       <c r="C72">
-        <v>7.748574551223056</v>
+        <v>7.584970343986411</v>
       </c>
       <c r="D72">
-        <v>20.98657455122306</v>
+        <v>21.01997034398641</v>
       </c>
       <c r="E72">
-        <v>8.790000000000003</v>
+        <v>8.987000000000002</v>
       </c>
       <c r="F72">
-        <v>13.79</v>
+        <v>13.987</v>
       </c>
       <c r="G72">
         <v>0.552</v>
@@ -7173,28 +7173,28 @@
         <v>3.581</v>
       </c>
       <c r="M72">
-        <v>0.7625870000000001</v>
+        <v>0.7734811</v>
       </c>
       <c r="N72">
-        <v>2.818413</v>
+        <v>2.8075189</v>
       </c>
       <c r="O72">
-        <v>0.7046032499999999</v>
+        <v>0.701879725</v>
       </c>
       <c r="P72">
-        <v>2.11380975</v>
+        <v>2.105639175</v>
       </c>
       <c r="Q72">
-        <v>2.34280975</v>
+        <v>2.334639175</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2015320169131713</v>
+        <v>0.2064138983211078</v>
       </c>
       <c r="T72">
-        <v>2.266090599778075</v>
+        <v>2.337127922655132</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.695857652962873</v>
+        <v>4.629718812780299</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08930728051312124</v>
+        <v>0.08912245595229108</v>
       </c>
       <c r="C73">
-        <v>7.584970343986409</v>
+        <v>7.421472591143834</v>
       </c>
       <c r="D73">
-        <v>21.01997034398641</v>
+        <v>21.05347259114383</v>
       </c>
       <c r="E73">
-        <v>8.986999999999998</v>
+        <v>9.184000000000001</v>
       </c>
       <c r="F73">
-        <v>13.987</v>
+        <v>14.184</v>
       </c>
       <c r="G73">
         <v>0.552</v>
@@ -7255,28 +7255,28 @@
         <v>3.581</v>
       </c>
       <c r="M73">
-        <v>0.7734810999999999</v>
+        <v>0.7843751999999999</v>
       </c>
       <c r="N73">
-        <v>2.8075189</v>
+        <v>2.7966248</v>
       </c>
       <c r="O73">
-        <v>0.701879725</v>
+        <v>0.6991562</v>
       </c>
       <c r="P73">
-        <v>2.105639175</v>
+        <v>2.0974686</v>
       </c>
       <c r="Q73">
-        <v>2.334639175</v>
+        <v>2.3264686</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2064138983211077</v>
+        <v>0.2116444855438967</v>
       </c>
       <c r="T73">
-        <v>2.337127922655131</v>
+        <v>2.413239340023404</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.6297188127803</v>
+        <v>4.565417162602795</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08912245595229108</v>
+        <v>0.08893763139146092</v>
       </c>
       <c r="C74">
-        <v>7.421472591143834</v>
+        <v>7.258081802518339</v>
       </c>
       <c r="D74">
-        <v>21.05347259114383</v>
+        <v>21.08708180251834</v>
       </c>
       <c r="E74">
-        <v>9.184000000000001</v>
+        <v>9.381</v>
       </c>
       <c r="F74">
-        <v>14.184</v>
+        <v>14.381</v>
       </c>
       <c r="G74">
         <v>0.552</v>
@@ -7337,28 +7337,28 @@
         <v>3.581</v>
       </c>
       <c r="M74">
-        <v>0.7843751999999999</v>
+        <v>0.7952693</v>
       </c>
       <c r="N74">
-        <v>2.7966248</v>
+        <v>2.7857307</v>
       </c>
       <c r="O74">
-        <v>0.6991562</v>
+        <v>0.6964326750000001</v>
       </c>
       <c r="P74">
-        <v>2.0974686</v>
+        <v>2.089298025</v>
       </c>
       <c r="Q74">
-        <v>2.3264686</v>
+        <v>2.318298025</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2116444855438967</v>
+        <v>0.2172625236720775</v>
       </c>
       <c r="T74">
-        <v>2.413239340023404</v>
+        <v>2.494988640159699</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.565417162602795</v>
+        <v>4.50287720147125</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08893763139146092</v>
+        <v>0.09014030683063076</v>
       </c>
       <c r="C75">
-        <v>7.258081802518339</v>
+        <v>6.844285568677691</v>
       </c>
       <c r="D75">
-        <v>21.08708180251834</v>
+        <v>20.87028556867769</v>
       </c>
       <c r="E75">
-        <v>9.381</v>
+        <v>9.577999999999999</v>
       </c>
       <c r="F75">
-        <v>14.381</v>
+        <v>14.578</v>
       </c>
       <c r="G75">
         <v>0.552</v>
@@ -7419,45 +7419,45 @@
         <v>3.581</v>
       </c>
       <c r="M75">
-        <v>0.7952693</v>
+        <v>0.8426084</v>
       </c>
       <c r="N75">
-        <v>2.7857307</v>
+        <v>2.7383916</v>
       </c>
       <c r="O75">
-        <v>0.6964326750000001</v>
+        <v>0.6845979</v>
       </c>
       <c r="P75">
-        <v>2.089298025</v>
+        <v>2.0537937</v>
       </c>
       <c r="Q75">
-        <v>2.318298025</v>
+        <v>2.2827937</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2172625236720775</v>
+        <v>0.2233127185793491</v>
       </c>
       <c r="T75">
-        <v>2.494988640159699</v>
+        <v>2.583026347998785</v>
       </c>
       <c r="U75">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.50287720147125</v>
+        <v>4.249898292017976</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09014030683063076</v>
+        <v>0.08997423226980061</v>
       </c>
       <c r="C76">
-        <v>6.844285568677691</v>
+        <v>6.676956782234093</v>
       </c>
       <c r="D76">
-        <v>20.87028556867769</v>
+        <v>20.89995678223409</v>
       </c>
       <c r="E76">
-        <v>9.577999999999999</v>
+        <v>9.774999999999999</v>
       </c>
       <c r="F76">
-        <v>14.578</v>
+        <v>14.775</v>
       </c>
       <c r="G76">
         <v>0.552</v>
@@ -7501,28 +7501,28 @@
         <v>3.581</v>
       </c>
       <c r="M76">
-        <v>0.8426084</v>
+        <v>0.8539949999999999</v>
       </c>
       <c r="N76">
-        <v>2.7383916</v>
+        <v>2.727005</v>
       </c>
       <c r="O76">
-        <v>0.6845979</v>
+        <v>0.68175125</v>
       </c>
       <c r="P76">
-        <v>2.0537937</v>
+        <v>2.04525375</v>
       </c>
       <c r="Q76">
-        <v>2.2827937</v>
+        <v>2.27425375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2233127185793491</v>
+        <v>0.2298469290792025</v>
       </c>
       <c r="T76">
-        <v>2.583026347998785</v>
+        <v>2.678107072464998</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.249898292017976</v>
+        <v>4.193232981457737</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08997423226980061</v>
+        <v>0.08980815770897047</v>
       </c>
       <c r="C77">
-        <v>6.676956782234093</v>
+        <v>6.509712482830933</v>
       </c>
       <c r="D77">
-        <v>20.89995678223409</v>
+        <v>20.92971248283093</v>
       </c>
       <c r="E77">
-        <v>9.774999999999999</v>
+        <v>9.972000000000001</v>
       </c>
       <c r="F77">
-        <v>14.775</v>
+        <v>14.972</v>
       </c>
       <c r="G77">
         <v>0.552</v>
@@ -7583,28 +7583,28 @@
         <v>3.581</v>
       </c>
       <c r="M77">
-        <v>0.8539949999999999</v>
+        <v>0.8653816000000001</v>
       </c>
       <c r="N77">
-        <v>2.727005</v>
+        <v>2.7156184</v>
       </c>
       <c r="O77">
-        <v>0.68175125</v>
+        <v>0.6789046</v>
       </c>
       <c r="P77">
-        <v>2.04525375</v>
+        <v>2.0367138</v>
       </c>
       <c r="Q77">
-        <v>2.27425375</v>
+        <v>2.2657138</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2298469290792025</v>
+        <v>0.2369256571207103</v>
       </c>
       <c r="T77">
-        <v>2.678107072464998</v>
+        <v>2.781111190636729</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.193232981457737</v>
+        <v>4.13805886328066</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08980815770897047</v>
+        <v>0.0896420831481403</v>
       </c>
       <c r="C78">
-        <v>6.509712482830933</v>
+        <v>6.342553031840545</v>
       </c>
       <c r="D78">
-        <v>20.92971248283093</v>
+        <v>20.95955303184055</v>
       </c>
       <c r="E78">
-        <v>9.972000000000001</v>
+        <v>10.169</v>
       </c>
       <c r="F78">
-        <v>14.972</v>
+        <v>15.169</v>
       </c>
       <c r="G78">
         <v>0.552</v>
@@ -7665,28 +7665,28 @@
         <v>3.581</v>
       </c>
       <c r="M78">
-        <v>0.8653816000000001</v>
+        <v>0.8767682000000001</v>
       </c>
       <c r="N78">
-        <v>2.7156184</v>
+        <v>2.7042318</v>
       </c>
       <c r="O78">
-        <v>0.6789046</v>
+        <v>0.6760579499999999</v>
       </c>
       <c r="P78">
-        <v>2.0367138</v>
+        <v>2.02817385</v>
       </c>
       <c r="Q78">
-        <v>2.2657138</v>
+        <v>2.25717385</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2369256571207103</v>
+        <v>0.2446199267310448</v>
       </c>
       <c r="T78">
-        <v>2.781111190636729</v>
+        <v>2.89307218864948</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.13805886328066</v>
+        <v>4.08431783908221</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0896420831481403</v>
+        <v>0.08947600858731014</v>
       </c>
       <c r="C79">
-        <v>6.342553031840545</v>
+        <v>6.175478792699117</v>
       </c>
       <c r="D79">
-        <v>20.95955303184055</v>
+        <v>20.98947879269912</v>
       </c>
       <c r="E79">
-        <v>10.169</v>
+        <v>10.366</v>
       </c>
       <c r="F79">
-        <v>15.169</v>
+        <v>15.366</v>
       </c>
       <c r="G79">
         <v>0.552</v>
@@ -7747,28 +7747,28 @@
         <v>3.581</v>
       </c>
       <c r="M79">
-        <v>0.8767682000000001</v>
+        <v>0.8881548</v>
       </c>
       <c r="N79">
-        <v>2.7042318</v>
+        <v>2.6928452</v>
       </c>
       <c r="O79">
-        <v>0.6760579499999999</v>
+        <v>0.6732113</v>
       </c>
       <c r="P79">
-        <v>2.02817385</v>
+        <v>2.0196339</v>
       </c>
       <c r="Q79">
-        <v>2.25717385</v>
+        <v>2.2486339</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2446199267310448</v>
+        <v>0.2530136753968643</v>
       </c>
       <c r="T79">
-        <v>2.89307218864948</v>
+        <v>3.015211459208844</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.08431783908221</v>
+        <v>4.031954789863208</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08947600858731014</v>
+        <v>0.09138368402648001</v>
       </c>
       <c r="C80">
-        <v>6.175478792699117</v>
+        <v>5.639789689904061</v>
       </c>
       <c r="D80">
-        <v>20.98947879269912</v>
+        <v>20.65078968990406</v>
       </c>
       <c r="E80">
-        <v>10.366</v>
+        <v>10.563</v>
       </c>
       <c r="F80">
-        <v>15.366</v>
+        <v>15.563</v>
       </c>
       <c r="G80">
         <v>0.552</v>
@@ -7829,45 +7829,45 @@
         <v>3.581</v>
       </c>
       <c r="M80">
-        <v>0.8881548</v>
+        <v>0.9540119</v>
       </c>
       <c r="N80">
-        <v>2.6928452</v>
+        <v>2.6269881</v>
       </c>
       <c r="O80">
-        <v>0.6732113</v>
+        <v>0.656747025</v>
       </c>
       <c r="P80">
-        <v>2.0196339</v>
+        <v>1.970241075</v>
       </c>
       <c r="Q80">
-        <v>2.2486339</v>
+        <v>2.199241075</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2530136753968643</v>
+        <v>0.2622068286975238</v>
       </c>
       <c r="T80">
-        <v>3.015211459208844</v>
+        <v>3.148983041250053</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.031954789863208</v>
+        <v>3.753621941193815</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09138368402648001</v>
+        <v>0.09124385946564983</v>
       </c>
       <c r="C81">
-        <v>5.639789689904061</v>
+        <v>5.467242521525995</v>
       </c>
       <c r="D81">
-        <v>20.65078968990406</v>
+        <v>20.67524252152599</v>
       </c>
       <c r="E81">
-        <v>10.563</v>
+        <v>10.76</v>
       </c>
       <c r="F81">
-        <v>15.563</v>
+        <v>15.76</v>
       </c>
       <c r="G81">
         <v>0.552</v>
@@ -7911,28 +7911,28 @@
         <v>3.581</v>
       </c>
       <c r="M81">
-        <v>0.9540119</v>
+        <v>0.9660879999999999</v>
       </c>
       <c r="N81">
-        <v>2.6269881</v>
+        <v>2.614912</v>
       </c>
       <c r="O81">
-        <v>0.656747025</v>
+        <v>0.653728</v>
       </c>
       <c r="P81">
-        <v>1.970241075</v>
+        <v>1.961184</v>
       </c>
       <c r="Q81">
-        <v>2.199241075</v>
+        <v>2.190184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2622068286975238</v>
+        <v>0.2723192973282492</v>
       </c>
       <c r="T81">
-        <v>3.148983041250053</v>
+        <v>3.296131781495383</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.753621941193815</v>
+        <v>3.706701666928893</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09124385946564983</v>
+        <v>0.09110403490481968</v>
       </c>
       <c r="C82">
-        <v>5.467242521525995</v>
+        <v>5.294753331545007</v>
       </c>
       <c r="D82">
-        <v>20.67524252152599</v>
+        <v>20.69975333154501</v>
       </c>
       <c r="E82">
-        <v>10.76</v>
+        <v>10.957</v>
       </c>
       <c r="F82">
-        <v>15.76</v>
+        <v>15.957</v>
       </c>
       <c r="G82">
         <v>0.552</v>
@@ -7993,28 +7993,28 @@
         <v>3.581</v>
       </c>
       <c r="M82">
-        <v>0.9660879999999999</v>
+        <v>0.9781641000000001</v>
       </c>
       <c r="N82">
-        <v>2.614912</v>
+        <v>2.6028359</v>
       </c>
       <c r="O82">
-        <v>0.653728</v>
+        <v>0.6507089749999999</v>
       </c>
       <c r="P82">
-        <v>1.961184</v>
+        <v>1.952126925</v>
       </c>
       <c r="Q82">
-        <v>2.190184</v>
+        <v>2.181126925</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2723192973282492</v>
+        <v>0.2834962363411563</v>
       </c>
       <c r="T82">
-        <v>3.296131781495383</v>
+        <v>3.458769862819168</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.706701666928893</v>
+        <v>3.660939917954461</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09110403490481968</v>
+        <v>0.09096421034398952</v>
       </c>
       <c r="C83">
-        <v>5.294753331545007</v>
+        <v>5.122322326408614</v>
       </c>
       <c r="D83">
-        <v>20.69975333154501</v>
+        <v>20.72432232640861</v>
       </c>
       <c r="E83">
-        <v>10.957</v>
+        <v>11.154</v>
       </c>
       <c r="F83">
-        <v>15.957</v>
+        <v>16.154</v>
       </c>
       <c r="G83">
         <v>0.552</v>
@@ -8075,28 +8075,28 @@
         <v>3.581</v>
       </c>
       <c r="M83">
-        <v>0.9781641000000001</v>
+        <v>0.9902402</v>
       </c>
       <c r="N83">
-        <v>2.6028359</v>
+        <v>2.5907598</v>
       </c>
       <c r="O83">
-        <v>0.6507089749999999</v>
+        <v>0.64768995</v>
       </c>
       <c r="P83">
-        <v>1.952126925</v>
+        <v>1.94306985</v>
       </c>
       <c r="Q83">
-        <v>2.181126925</v>
+        <v>2.17206985</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2834962363411563</v>
+        <v>0.2959150574666085</v>
       </c>
       <c r="T83">
-        <v>3.458769862819168</v>
+        <v>3.639478842067819</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.660939917954461</v>
+        <v>3.616294309198919</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09096421034398952</v>
+        <v>0.09082438578315938</v>
       </c>
       <c r="C84">
-        <v>5.122322326408614</v>
+        <v>4.949949713545671</v>
       </c>
       <c r="D84">
-        <v>20.72432232640861</v>
+        <v>20.74894971354567</v>
       </c>
       <c r="E84">
-        <v>11.154</v>
+        <v>11.351</v>
       </c>
       <c r="F84">
-        <v>16.154</v>
+        <v>16.351</v>
       </c>
       <c r="G84">
         <v>0.552</v>
@@ -8157,28 +8157,28 @@
         <v>3.581</v>
       </c>
       <c r="M84">
-        <v>0.9902402</v>
+        <v>1.0023163</v>
       </c>
       <c r="N84">
-        <v>2.5907598</v>
+        <v>2.5786837</v>
       </c>
       <c r="O84">
-        <v>0.64768995</v>
+        <v>0.644670925</v>
       </c>
       <c r="P84">
-        <v>1.94306985</v>
+        <v>1.934012775</v>
       </c>
       <c r="Q84">
-        <v>2.17206985</v>
+        <v>2.163012775</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2959150574666085</v>
+        <v>0.3097949163715258</v>
       </c>
       <c r="T84">
-        <v>3.639478842067819</v>
+        <v>3.841447701228076</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.616294309198919</v>
+        <v>3.572724498244716</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09082438578315938</v>
+        <v>0.09068456122232921</v>
       </c>
       <c r="C85">
-        <v>4.949949713545671</v>
+        <v>4.777635701372152</v>
       </c>
       <c r="D85">
-        <v>20.74894971354567</v>
+        <v>20.77363570137215</v>
       </c>
       <c r="E85">
-        <v>11.351</v>
+        <v>11.548</v>
       </c>
       <c r="F85">
-        <v>16.351</v>
+        <v>16.548</v>
       </c>
       <c r="G85">
         <v>0.552</v>
@@ -8239,28 +8239,28 @@
         <v>3.581</v>
       </c>
       <c r="M85">
-        <v>1.0023163</v>
+        <v>1.0143924</v>
       </c>
       <c r="N85">
-        <v>2.5786837</v>
+        <v>2.5666076</v>
       </c>
       <c r="O85">
-        <v>0.644670925</v>
+        <v>0.6416518999999999</v>
       </c>
       <c r="P85">
-        <v>1.934012775</v>
+        <v>1.9249557</v>
       </c>
       <c r="Q85">
-        <v>2.163012775</v>
+        <v>2.1539557</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3097949163715258</v>
+        <v>0.3254097576395577</v>
       </c>
       <c r="T85">
-        <v>3.841447701228076</v>
+        <v>4.068662667783364</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.572724498244716</v>
+        <v>3.530192063741802</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09068456122232921</v>
+        <v>0.09232973666149907</v>
       </c>
       <c r="C86">
-        <v>4.777635701372155</v>
+        <v>4.293849453638551</v>
       </c>
       <c r="D86">
-        <v>20.77363570137215</v>
+        <v>20.48684945363855</v>
       </c>
       <c r="E86">
-        <v>11.548</v>
+        <v>11.745</v>
       </c>
       <c r="F86">
-        <v>16.548</v>
+        <v>16.745</v>
       </c>
       <c r="G86">
         <v>0.552</v>
@@ -8321,45 +8321,45 @@
         <v>3.581</v>
       </c>
       <c r="M86">
-        <v>1.0143924</v>
+        <v>1.0733545</v>
       </c>
       <c r="N86">
-        <v>2.5666076</v>
+        <v>2.5076455</v>
       </c>
       <c r="O86">
-        <v>0.6416519000000001</v>
+        <v>0.6269113749999999</v>
       </c>
       <c r="P86">
-        <v>1.9249557</v>
+        <v>1.880734125</v>
       </c>
       <c r="Q86">
-        <v>2.1539557</v>
+        <v>2.109734125</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3254097576395575</v>
+        <v>0.343106577743327</v>
       </c>
       <c r="T86">
-        <v>4.068662667783362</v>
+        <v>4.326172963212689</v>
       </c>
       <c r="U86">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.530192063741803</v>
+        <v>3.336269610832209</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09232973666149907</v>
+        <v>0.09221091210066891</v>
       </c>
       <c r="C87">
-        <v>4.293849453638551</v>
+        <v>4.117297331350954</v>
       </c>
       <c r="D87">
-        <v>20.48684945363855</v>
+        <v>20.50729733135096</v>
       </c>
       <c r="E87">
-        <v>11.745</v>
+        <v>11.942</v>
       </c>
       <c r="F87">
-        <v>16.745</v>
+        <v>16.942</v>
       </c>
       <c r="G87">
         <v>0.552</v>
@@ -8403,28 +8403,28 @@
         <v>3.581</v>
       </c>
       <c r="M87">
-        <v>1.0733545</v>
+        <v>1.0859822</v>
       </c>
       <c r="N87">
-        <v>2.5076455</v>
+        <v>2.4950178</v>
       </c>
       <c r="O87">
-        <v>0.6269113749999999</v>
+        <v>0.62375445</v>
       </c>
       <c r="P87">
-        <v>1.880734125</v>
+        <v>1.87126335</v>
       </c>
       <c r="Q87">
-        <v>2.109734125</v>
+        <v>2.10026335</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.343106577743327</v>
+        <v>0.3633315150047778</v>
       </c>
       <c r="T87">
-        <v>4.326172963212689</v>
+        <v>4.620470443703348</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.336269610832209</v>
+        <v>3.297475778148113</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09221091210066891</v>
+        <v>0.09209208753983875</v>
       </c>
       <c r="C88">
-        <v>4.117297331350954</v>
+        <v>3.940786067804591</v>
       </c>
       <c r="D88">
-        <v>20.50729733135096</v>
+        <v>20.52778606780459</v>
       </c>
       <c r="E88">
-        <v>11.942</v>
+        <v>12.139</v>
       </c>
       <c r="F88">
-        <v>16.942</v>
+        <v>17.139</v>
       </c>
       <c r="G88">
         <v>0.552</v>
@@ -8485,28 +8485,28 @@
         <v>3.581</v>
       </c>
       <c r="M88">
-        <v>1.0859822</v>
+        <v>1.0986099</v>
       </c>
       <c r="N88">
-        <v>2.4950178</v>
+        <v>2.4823901</v>
       </c>
       <c r="O88">
-        <v>0.62375445</v>
+        <v>0.620597525</v>
       </c>
       <c r="P88">
-        <v>1.87126335</v>
+        <v>1.861792575</v>
       </c>
       <c r="Q88">
-        <v>2.10026335</v>
+        <v>2.090792575</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3633315150047778</v>
+        <v>0.3866679810756826</v>
       </c>
       <c r="T88">
-        <v>4.620470443703348</v>
+        <v>4.960044459654108</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.297475778148113</v>
+        <v>3.259573757709629</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09209208753983875</v>
+        <v>0.0919732629790086</v>
       </c>
       <c r="C89">
-        <v>3.940786067804591</v>
+        <v>3.764315785587211</v>
       </c>
       <c r="D89">
-        <v>20.52778606780459</v>
+        <v>20.54831578558721</v>
       </c>
       <c r="E89">
-        <v>12.139</v>
+        <v>12.336</v>
       </c>
       <c r="F89">
-        <v>17.139</v>
+        <v>17.336</v>
       </c>
       <c r="G89">
         <v>0.552</v>
@@ -8567,28 +8567,28 @@
         <v>3.581</v>
       </c>
       <c r="M89">
-        <v>1.0986099</v>
+        <v>1.1112376</v>
       </c>
       <c r="N89">
-        <v>2.4823901</v>
+        <v>2.4697624</v>
       </c>
       <c r="O89">
-        <v>0.620597525</v>
+        <v>0.6174406</v>
       </c>
       <c r="P89">
-        <v>1.861792575</v>
+        <v>1.8523218</v>
       </c>
       <c r="Q89">
-        <v>2.090792575</v>
+        <v>2.0813218</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3866679810756826</v>
+        <v>0.4138938581584049</v>
       </c>
       <c r="T89">
-        <v>4.960044459654108</v>
+        <v>5.356214144929996</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.259573757709629</v>
+        <v>3.222533146826565</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0919732629790086</v>
+        <v>0.09185443841817845</v>
       </c>
       <c r="C90">
-        <v>3.764315785587211</v>
+        <v>3.58788660777746</v>
       </c>
       <c r="D90">
-        <v>20.54831578558721</v>
+        <v>20.56888660777746</v>
       </c>
       <c r="E90">
-        <v>12.336</v>
+        <v>12.533</v>
       </c>
       <c r="F90">
-        <v>17.336</v>
+        <v>17.533</v>
       </c>
       <c r="G90">
         <v>0.552</v>
@@ -8649,28 +8649,28 @@
         <v>3.581</v>
       </c>
       <c r="M90">
-        <v>1.1112376</v>
+        <v>1.1238653</v>
       </c>
       <c r="N90">
-        <v>2.4697624</v>
+        <v>2.4571347</v>
       </c>
       <c r="O90">
-        <v>0.6174406</v>
+        <v>0.614283675</v>
       </c>
       <c r="P90">
-        <v>1.8523218</v>
+        <v>1.842851025</v>
       </c>
       <c r="Q90">
-        <v>2.0813218</v>
+        <v>2.071851025</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4138938581584049</v>
+        <v>0.4460698947107131</v>
       </c>
       <c r="T90">
-        <v>5.356214144929996</v>
+        <v>5.824414682074226</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.222533146826565</v>
+        <v>3.186324909221772</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09185443841817845</v>
+        <v>0.09173561385734828</v>
       </c>
       <c r="C91">
-        <v>3.58788660777746</v>
+        <v>3.411498657947345</v>
       </c>
       <c r="D91">
-        <v>20.56888660777746</v>
+        <v>20.58949865794735</v>
       </c>
       <c r="E91">
-        <v>12.533</v>
+        <v>12.73</v>
       </c>
       <c r="F91">
-        <v>17.533</v>
+        <v>17.73</v>
       </c>
       <c r="G91">
         <v>0.552</v>
@@ -8731,28 +8731,28 @@
         <v>3.581</v>
       </c>
       <c r="M91">
-        <v>1.1238653</v>
+        <v>1.136493</v>
       </c>
       <c r="N91">
-        <v>2.4571347</v>
+        <v>2.444507</v>
       </c>
       <c r="O91">
-        <v>0.614283675</v>
+        <v>0.6111267499999999</v>
       </c>
       <c r="P91">
-        <v>1.842851025</v>
+        <v>1.83338025</v>
       </c>
       <c r="Q91">
-        <v>2.071851025</v>
+        <v>2.06238025</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4460698947107131</v>
+        <v>0.4846811385734829</v>
       </c>
       <c r="T91">
-        <v>5.824414682074226</v>
+        <v>6.386255326647304</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.186324909221772</v>
+        <v>3.150921299119308</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09173561385734828</v>
+        <v>0.09161678929651812</v>
       </c>
       <c r="C92">
-        <v>3.411498657947345</v>
+        <v>3.23515206016468</v>
       </c>
       <c r="D92">
-        <v>20.58949865794735</v>
+        <v>20.61015206016468</v>
       </c>
       <c r="E92">
-        <v>12.73</v>
+        <v>12.927</v>
       </c>
       <c r="F92">
-        <v>17.73</v>
+        <v>17.927</v>
       </c>
       <c r="G92">
         <v>0.552</v>
@@ -8813,28 +8813,28 @@
         <v>3.581</v>
       </c>
       <c r="M92">
-        <v>1.136493</v>
+        <v>1.1491207</v>
       </c>
       <c r="N92">
-        <v>2.444507</v>
+        <v>2.4318793</v>
       </c>
       <c r="O92">
-        <v>0.6111267499999999</v>
+        <v>0.607969825</v>
       </c>
       <c r="P92">
-        <v>1.83338025</v>
+        <v>1.823909475</v>
       </c>
       <c r="Q92">
-        <v>2.06238025</v>
+        <v>2.052909475</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4846811385734829</v>
+        <v>0.5318726588502015</v>
       </c>
       <c r="T92">
-        <v>6.386255326647304</v>
+        <v>7.072949447792176</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.150921299119308</v>
+        <v>3.116295790337777</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09161678929651812</v>
+        <v>0.09149796473568798</v>
       </c>
       <c r="C93">
-        <v>3.23515206016468</v>
+        <v>3.058846938995572</v>
       </c>
       <c r="D93">
-        <v>20.61015206016468</v>
+        <v>20.63084693899557</v>
       </c>
       <c r="E93">
-        <v>12.927</v>
+        <v>13.124</v>
       </c>
       <c r="F93">
-        <v>17.927</v>
+        <v>18.124</v>
       </c>
       <c r="G93">
         <v>0.552</v>
@@ -8895,28 +8895,28 @@
         <v>3.581</v>
       </c>
       <c r="M93">
-        <v>1.1491207</v>
+        <v>1.1617484</v>
       </c>
       <c r="N93">
-        <v>2.4318793</v>
+        <v>2.4192516</v>
       </c>
       <c r="O93">
-        <v>0.607969825</v>
+        <v>0.6048129</v>
       </c>
       <c r="P93">
-        <v>1.823909475</v>
+        <v>1.8144387</v>
       </c>
       <c r="Q93">
-        <v>2.052909475</v>
+        <v>2.0434387</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5318726588502015</v>
+        <v>0.5908620591960999</v>
       </c>
       <c r="T93">
-        <v>7.072949447792176</v>
+        <v>7.931317099223268</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.116295790337777</v>
+        <v>3.082423010008019</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09149796473568798</v>
+        <v>0.09137914017485782</v>
       </c>
       <c r="C94">
-        <v>3.058846938995572</v>
+        <v>2.882583419506989</v>
       </c>
       <c r="D94">
-        <v>20.63084693899557</v>
+        <v>20.65158341950699</v>
       </c>
       <c r="E94">
-        <v>13.124</v>
+        <v>13.321</v>
       </c>
       <c r="F94">
-        <v>18.124</v>
+        <v>18.321</v>
       </c>
       <c r="G94">
         <v>0.552</v>
@@ -8977,28 +8977,28 @@
         <v>3.581</v>
       </c>
       <c r="M94">
-        <v>1.1617484</v>
+        <v>1.1743761</v>
       </c>
       <c r="N94">
-        <v>2.4192516</v>
+        <v>2.4066239</v>
       </c>
       <c r="O94">
-        <v>0.6048129</v>
+        <v>0.6016559749999999</v>
       </c>
       <c r="P94">
-        <v>1.8144387</v>
+        <v>1.804967925</v>
       </c>
       <c r="Q94">
-        <v>2.0434387</v>
+        <v>2.033967925</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5908620591960999</v>
+        <v>0.6667055739265406</v>
       </c>
       <c r="T94">
-        <v>7.931317099223268</v>
+        <v>9.034932651063242</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.082423010008019</v>
+        <v>3.049278676567072</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09137914017485782</v>
+        <v>0.09126031561402764</v>
       </c>
       <c r="C95">
-        <v>2.882583419506989</v>
+        <v>2.706361627269203</v>
       </c>
       <c r="D95">
-        <v>20.65158341950699</v>
+        <v>20.6723616272692</v>
       </c>
       <c r="E95">
-        <v>13.321</v>
+        <v>13.518</v>
       </c>
       <c r="F95">
-        <v>18.321</v>
+        <v>18.518</v>
       </c>
       <c r="G95">
         <v>0.552</v>
@@ -9059,28 +9059,28 @@
         <v>3.581</v>
       </c>
       <c r="M95">
-        <v>1.1743761</v>
+        <v>1.1870038</v>
       </c>
       <c r="N95">
-        <v>2.4066239</v>
+        <v>2.3939962</v>
       </c>
       <c r="O95">
-        <v>0.6016559749999999</v>
+        <v>0.59849905</v>
       </c>
       <c r="P95">
-        <v>1.804967925</v>
+        <v>1.79549715</v>
       </c>
       <c r="Q95">
-        <v>2.033967925</v>
+        <v>2.02449715</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6667055739265406</v>
+        <v>0.7678302602337947</v>
       </c>
       <c r="T95">
-        <v>9.034932651063242</v>
+        <v>10.50642005351654</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.049278676567072</v>
+        <v>3.016839541709976</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09126031561402764</v>
+        <v>0.0966989910531975</v>
       </c>
       <c r="C96">
-        <v>2.706361627269203</v>
+        <v>1.59928329643347</v>
       </c>
       <c r="D96">
-        <v>20.6723616272692</v>
+        <v>19.76228329643347</v>
       </c>
       <c r="E96">
-        <v>13.518</v>
+        <v>13.715</v>
       </c>
       <c r="F96">
-        <v>18.518</v>
+        <v>18.715</v>
       </c>
       <c r="G96">
         <v>0.552</v>
@@ -9141,45 +9141,45 @@
         <v>3.581</v>
       </c>
       <c r="M96">
-        <v>1.1870038</v>
+        <v>1.3456085</v>
       </c>
       <c r="N96">
-        <v>2.3939962</v>
+        <v>2.2353915</v>
       </c>
       <c r="O96">
-        <v>0.59849905</v>
+        <v>0.558847875</v>
       </c>
       <c r="P96">
-        <v>1.79549715</v>
+        <v>1.676543625</v>
       </c>
       <c r="Q96">
-        <v>2.02449715</v>
+        <v>1.905543625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7678302602337947</v>
+        <v>0.9094048210639512</v>
       </c>
       <c r="T96">
-        <v>10.50642005351654</v>
+        <v>12.56650241695116</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.016839541709976</v>
+        <v>2.661249538777438</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0966989910531975</v>
+        <v>0.09663866649236735</v>
       </c>
       <c r="C97">
-        <v>1.59928329643347</v>
+        <v>1.411938000059465</v>
       </c>
       <c r="D97">
-        <v>19.76228329643347</v>
+        <v>19.77193800005946</v>
       </c>
       <c r="E97">
-        <v>13.715</v>
+        <v>13.912</v>
       </c>
       <c r="F97">
-        <v>18.715</v>
+        <v>18.912</v>
       </c>
       <c r="G97">
         <v>0.552</v>
@@ -9223,28 +9223,28 @@
         <v>3.581</v>
       </c>
       <c r="M97">
-        <v>1.3456085</v>
+        <v>1.3597728</v>
       </c>
       <c r="N97">
-        <v>2.2353915</v>
+        <v>2.2212272</v>
       </c>
       <c r="O97">
-        <v>0.558847875</v>
+        <v>0.5553068</v>
       </c>
       <c r="P97">
-        <v>1.676543625</v>
+        <v>1.6659204</v>
       </c>
       <c r="Q97">
-        <v>1.905543625</v>
+        <v>1.8949204</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9094048210639512</v>
+        <v>1.121766662309186</v>
       </c>
       <c r="T97">
-        <v>12.56650241695116</v>
+        <v>15.65662596210309</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.661249538777438</v>
+        <v>2.633528189415173</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09663866649236735</v>
+        <v>0.09657834193153719</v>
       </c>
       <c r="C98">
-        <v>1.411938000059465</v>
+        <v>1.224602141751046</v>
       </c>
       <c r="D98">
-        <v>19.77193800005946</v>
+        <v>19.78160214175104</v>
       </c>
       <c r="E98">
-        <v>13.912</v>
+        <v>14.109</v>
       </c>
       <c r="F98">
-        <v>18.912</v>
+        <v>19.109</v>
       </c>
       <c r="G98">
         <v>0.552</v>
@@ -9305,28 +9305,28 @@
         <v>3.581</v>
       </c>
       <c r="M98">
-        <v>1.3597728</v>
+        <v>1.3739371</v>
       </c>
       <c r="N98">
-        <v>2.2212272</v>
+        <v>2.2070629</v>
       </c>
       <c r="O98">
-        <v>0.5553068</v>
+        <v>0.551765725</v>
       </c>
       <c r="P98">
-        <v>1.6659204</v>
+        <v>1.655297175</v>
       </c>
       <c r="Q98">
-        <v>1.8949204</v>
+        <v>1.884297175</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.121766662309183</v>
+        <v>1.475703064384572</v>
       </c>
       <c r="T98">
-        <v>15.65662596210305</v>
+        <v>20.80683187068958</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.633528189415173</v>
+        <v>2.606378414266563</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09657834193153719</v>
+        <v>0.09651801737070703</v>
       </c>
       <c r="C99">
-        <v>1.224602141751046</v>
+        <v>1.037275735354417</v>
       </c>
       <c r="D99">
-        <v>19.78160214175104</v>
+        <v>19.79127573535441</v>
       </c>
       <c r="E99">
-        <v>14.109</v>
+        <v>14.306</v>
       </c>
       <c r="F99">
-        <v>19.109</v>
+        <v>19.306</v>
       </c>
       <c r="G99">
         <v>0.552</v>
@@ -9387,28 +9387,28 @@
         <v>3.581</v>
       </c>
       <c r="M99">
-        <v>1.3739371</v>
+        <v>1.3881014</v>
       </c>
       <c r="N99">
-        <v>2.2070629</v>
+        <v>2.1928986</v>
       </c>
       <c r="O99">
-        <v>0.551765725</v>
+        <v>0.5482246500000001</v>
       </c>
       <c r="P99">
-        <v>1.655297175</v>
+        <v>1.64467395</v>
       </c>
       <c r="Q99">
-        <v>1.884297175</v>
+        <v>1.87367395</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.475703064384572</v>
+        <v>2.18357586853535</v>
       </c>
       <c r="T99">
-        <v>20.80683187068958</v>
+        <v>31.10724368786265</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.606378414266563</v>
+        <v>2.579782716161803</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09651801737070703</v>
+        <v>0.09645769280987687</v>
       </c>
       <c r="C100">
-        <v>1.037275735354417</v>
+        <v>0.8499587947428751</v>
       </c>
       <c r="D100">
-        <v>19.79127573535441</v>
+        <v>19.80095879474288</v>
       </c>
       <c r="E100">
-        <v>14.306</v>
+        <v>14.503</v>
       </c>
       <c r="F100">
-        <v>19.306</v>
+        <v>19.503</v>
       </c>
       <c r="G100">
         <v>0.552</v>
@@ -9469,28 +9469,28 @@
         <v>3.581</v>
       </c>
       <c r="M100">
-        <v>1.3881014</v>
+        <v>1.4022657</v>
       </c>
       <c r="N100">
-        <v>2.1928986</v>
+        <v>2.1787343</v>
       </c>
       <c r="O100">
-        <v>0.5482246500000001</v>
+        <v>0.544683575</v>
       </c>
       <c r="P100">
-        <v>1.64467395</v>
+        <v>1.634050725</v>
       </c>
       <c r="Q100">
-        <v>1.87367395</v>
+        <v>1.863050725</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.18357586853535</v>
+        <v>4.307194280987684</v>
       </c>
       <c r="T100">
-        <v>31.10724368786265</v>
+        <v>62.00847913938183</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.579782716161803</v>
+        <v>2.553724304887441</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09645769280987687</v>
-      </c>
-      <c r="C101">
-        <v>0.8499587947428751</v>
-      </c>
-      <c r="D101">
-        <v>19.80095879474288</v>
-      </c>
-      <c r="E101">
-        <v>14.503</v>
-      </c>
-      <c r="F101">
-        <v>19.503</v>
-      </c>
-      <c r="G101">
-        <v>0.552</v>
-      </c>
-      <c r="H101">
-        <v>14.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.81</v>
-      </c>
-      <c r="K101">
-        <v>0.229</v>
-      </c>
-      <c r="L101">
-        <v>3.581</v>
-      </c>
-      <c r="M101">
-        <v>1.4022657</v>
-      </c>
-      <c r="N101">
-        <v>2.1787343</v>
-      </c>
-      <c r="O101">
-        <v>0.544683575</v>
-      </c>
-      <c r="P101">
-        <v>1.634050725</v>
-      </c>
-      <c r="Q101">
-        <v>1.863050725</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.307194280987684</v>
-      </c>
-      <c r="T101">
-        <v>62.00847913938183</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.053925</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.553724304887441</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
